--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2091">
   <si>
     <t>en</t>
   </si>
@@ -5890,391 +5890,394 @@
     <t>Sukta stebuklų šalis</t>
   </si>
   <si>
+    <t>ULTRAKILL</t>
+  </si>
+  <si>
+    <t>Umineko - When They Cry</t>
+  </si>
+  <si>
+    <t>Umineko - Kai jie verkia</t>
+  </si>
+  <si>
+    <t>Undertale</t>
+  </si>
+  <si>
+    <t>Undertale AU</t>
+  </si>
+  <si>
+    <t>Undertale Yellow</t>
+  </si>
+  <si>
+    <t>Undertale geltonas</t>
+  </si>
+  <si>
+    <t>Universal Symbol</t>
+  </si>
+  <si>
+    <t>Universalus simbolis</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>Į viršų</t>
+  </si>
+  <si>
+    <t>Urban Wildlife</t>
+  </si>
+  <si>
+    <t>Miesto laukinė gyvūnija ir augalija</t>
+  </si>
+  <si>
+    <t>V for Vendetta</t>
+  </si>
+  <si>
+    <t>Valentines</t>
+  </si>
+  <si>
+    <t>Valentinas</t>
+  </si>
+  <si>
+    <t>Valorant</t>
+  </si>
+  <si>
+    <t>Vanilla (removed)</t>
+  </si>
+  <si>
+    <t>Vanilė (pašalinta)</t>
+  </si>
+  <si>
+    <t>Vanilla Block</t>
+  </si>
+  <si>
+    <t>Vanilės blokas</t>
+  </si>
+  <si>
+    <t>Vanilla Food</t>
+  </si>
+  <si>
+    <t>Vanilės maistas</t>
+  </si>
+  <si>
+    <t>Vanilla Helmet</t>
+  </si>
+  <si>
+    <t>Vanilės šalmas</t>
+  </si>
+  <si>
+    <t>Vanilla Item</t>
+  </si>
+  <si>
+    <t>Vanilės elementas</t>
+  </si>
+  <si>
+    <t>Vanilla Mob</t>
+  </si>
+  <si>
+    <t>Vanilinė mafija</t>
+  </si>
+  <si>
+    <t>Vault Hunters</t>
+  </si>
+  <si>
+    <t>Saugyklų medžiotojai</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>Daržovės</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Transporto priemonė</t>
+  </si>
+  <si>
+    <t>Vikings</t>
+  </si>
+  <si>
+    <t>Vikingai</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Kaimo gyventojas</t>
+  </si>
+  <si>
+    <t>Villager (Desert)</t>
+  </si>
+  <si>
+    <t>Kaimo gyventojas (dykuma)</t>
+  </si>
+  <si>
+    <t>Villager (Jungle)</t>
+  </si>
+  <si>
+    <t>Kaimo gyventojas (džiunglės)</t>
+  </si>
+  <si>
+    <t>Villager (Plains)</t>
+  </si>
+  <si>
+    <t>Kaimo gyventojas (lygumos)</t>
+  </si>
+  <si>
+    <t>Villager (Savanna)</t>
+  </si>
+  <si>
+    <t>Kaimo gyventojas (Savanna)</t>
+  </si>
+  <si>
+    <t>Villager (Snowy Tundra)</t>
+  </si>
+  <si>
+    <t>Kaimo gyventojas (Snieguotoji tundra)</t>
+  </si>
+  <si>
+    <t>Villager (Swamp)</t>
+  </si>
+  <si>
+    <t>Kaimo gyventojas (Pelkė)</t>
+  </si>
+  <si>
+    <t>Villager (Taiga)</t>
+  </si>
+  <si>
+    <t>Kaimo gyventojas (Taiga)</t>
+  </si>
+  <si>
+    <t>Virtual Youtuber</t>
+  </si>
+  <si>
+    <t>Virtualus youtuberis</t>
+  </si>
+  <si>
+    <t>Vocaloid</t>
+  </si>
+  <si>
+    <t>Voltron</t>
+  </si>
+  <si>
+    <t>Voltronas</t>
+  </si>
+  <si>
+    <t>Wakfu</t>
+  </si>
+  <si>
+    <t>Walking Dead</t>
+  </si>
+  <si>
+    <t>Vaikščiojantys numirėliai</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>Wallace and Gromit</t>
+  </si>
+  <si>
+    <t>Volisas ir Gromitas</t>
+  </si>
+  <si>
+    <t>War of the Worlds</t>
+  </si>
+  <si>
+    <t>Pasaulių karas</t>
+  </si>
+  <si>
+    <t>Warcraft</t>
+  </si>
+  <si>
+    <t>Warframe</t>
+  </si>
+  <si>
+    <t>Warhammer</t>
+  </si>
+  <si>
+    <t>Warrior Cats</t>
+  </si>
+  <si>
+    <t>Kariaujančios katės</t>
+  </si>
+  <si>
+    <t>We Bear Bears</t>
+  </si>
+  <si>
+    <t>Mes nešame meškiukus</t>
+  </si>
+  <si>
+    <t>We Happy Few</t>
+  </si>
+  <si>
+    <t>Mes laimingi nedaugelis</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>Orai</t>
+  </si>
+  <si>
+    <t>Welcome Home</t>
+  </si>
+  <si>
+    <t>Sveiki atvykę į namus</t>
+  </si>
+  <si>
+    <t>Who is this?</t>
+  </si>
+  <si>
+    <t>Kas tai?</t>
+  </si>
+  <si>
+    <t>Wild Update</t>
+  </si>
+  <si>
+    <t>Laukinis atnaujinimas</t>
+  </si>
+  <si>
+    <t>Wings of Fire</t>
+  </si>
+  <si>
+    <t>Ugnies sparnai</t>
+  </si>
+  <si>
+    <t>Winnie the Pooh</t>
+  </si>
+  <si>
+    <t>Meškiukas Pūkuotukas</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>Žiema</t>
+  </si>
+  <si>
+    <t>Witcher</t>
+  </si>
+  <si>
+    <t>Wonderful Wonder World</t>
+  </si>
+  <si>
+    <t>Nuostabus stebuklų pasaulis</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>Mediena</t>
+  </si>
+  <si>
+    <t>Wool</t>
+  </si>
+  <si>
+    <t>Vilna</t>
+  </si>
+  <si>
+    <t>Work Safety Helmet</t>
+  </si>
+  <si>
+    <t>Darbo saugos šalmas</t>
+  </si>
+  <si>
+    <t>Wreck It Ralph</t>
+  </si>
+  <si>
+    <t>Išardyti Ralfą (Wreck It Ralph)</t>
+  </si>
+  <si>
+    <t>Wybel</t>
+  </si>
+  <si>
+    <t>Wynncraft</t>
+  </si>
+  <si>
+    <t>X-Men</t>
+  </si>
+  <si>
+    <t>X-Menai</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles</t>
+  </si>
+  <si>
+    <t>"Xenoblade Chronicles</t>
+  </si>
+  <si>
+    <t>Yandere Simulator</t>
+  </si>
+  <si>
+    <t>Yandere simuliatorius</t>
+  </si>
+  <si>
+    <t>Yellow Submarine</t>
+  </si>
+  <si>
+    <t>Geltonasis povandeninis laivas</t>
+  </si>
+  <si>
+    <t>Yokai</t>
+  </si>
+  <si>
+    <t>Yooka Laylee</t>
+  </si>
+  <si>
+    <t>"Yooka Laylee</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Jaunimas</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>"Youtube"</t>
+  </si>
+  <si>
+    <t>Yu-Gi-Oh</t>
+  </si>
+  <si>
+    <t>Yume Nikki</t>
+  </si>
+  <si>
+    <t>Zero no Tsukaima</t>
+  </si>
+  <si>
+    <t>Zero Wing</t>
+  </si>
+  <si>
+    <t>Nulinis sparnas</t>
+  </si>
+  <si>
+    <t>Zodiac Sign</t>
+  </si>
+  <si>
+    <t>Zodiako ženklas</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>Zombie (Vanilla)</t>
+  </si>
+  <si>
+    <t>Zombis (vanilė)</t>
+  </si>
+  <si>
+    <t>Zootopia</t>
+  </si>
+  <si>
+    <t>Zootopija</t>
+  </si>
+  <si>
     <t>Ultrakill</t>
-  </si>
-  <si>
-    <t>Umineko - When They Cry</t>
-  </si>
-  <si>
-    <t>Umineko - Kai jie verkia</t>
-  </si>
-  <si>
-    <t>Undertale</t>
-  </si>
-  <si>
-    <t>Undertale AU</t>
-  </si>
-  <si>
-    <t>Undertale Yellow</t>
-  </si>
-  <si>
-    <t>Undertale geltonas</t>
-  </si>
-  <si>
-    <t>Universal Symbol</t>
-  </si>
-  <si>
-    <t>Universalus simbolis</t>
-  </si>
-  <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>Į viršų</t>
-  </si>
-  <si>
-    <t>Urban Wildlife</t>
-  </si>
-  <si>
-    <t>Miesto laukinė gyvūnija ir augalija</t>
-  </si>
-  <si>
-    <t>V for Vendetta</t>
-  </si>
-  <si>
-    <t>Valentines</t>
-  </si>
-  <si>
-    <t>Valentinas</t>
-  </si>
-  <si>
-    <t>Valorant</t>
-  </si>
-  <si>
-    <t>Vanilla (removed)</t>
-  </si>
-  <si>
-    <t>Vanilė (pašalinta)</t>
-  </si>
-  <si>
-    <t>Vanilla Block</t>
-  </si>
-  <si>
-    <t>Vanilės blokas</t>
-  </si>
-  <si>
-    <t>Vanilla Food</t>
-  </si>
-  <si>
-    <t>Vanilės maistas</t>
-  </si>
-  <si>
-    <t>Vanilla Helmet</t>
-  </si>
-  <si>
-    <t>Vanilės šalmas</t>
-  </si>
-  <si>
-    <t>Vanilla Item</t>
-  </si>
-  <si>
-    <t>Vanilės elementas</t>
-  </si>
-  <si>
-    <t>Vanilla Mob</t>
-  </si>
-  <si>
-    <t>Vanilinė mafija</t>
-  </si>
-  <si>
-    <t>Vault Hunters</t>
-  </si>
-  <si>
-    <t>Saugyklų medžiotojai</t>
-  </si>
-  <si>
-    <t>Vegetable</t>
-  </si>
-  <si>
-    <t>Daržovės</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>Transporto priemonė</t>
-  </si>
-  <si>
-    <t>Vikings</t>
-  </si>
-  <si>
-    <t>Vikingai</t>
-  </si>
-  <si>
-    <t>Villager</t>
-  </si>
-  <si>
-    <t>Kaimo gyventojas</t>
-  </si>
-  <si>
-    <t>Villager (Desert)</t>
-  </si>
-  <si>
-    <t>Kaimo gyventojas (dykuma)</t>
-  </si>
-  <si>
-    <t>Villager (Jungle)</t>
-  </si>
-  <si>
-    <t>Kaimo gyventojas (džiunglės)</t>
-  </si>
-  <si>
-    <t>Villager (Plains)</t>
-  </si>
-  <si>
-    <t>Kaimo gyventojas (lygumos)</t>
-  </si>
-  <si>
-    <t>Villager (Savanna)</t>
-  </si>
-  <si>
-    <t>Kaimo gyventojas (Savanna)</t>
-  </si>
-  <si>
-    <t>Villager (Snowy Tundra)</t>
-  </si>
-  <si>
-    <t>Kaimo gyventojas (Snieguotoji tundra)</t>
-  </si>
-  <si>
-    <t>Villager (Swamp)</t>
-  </si>
-  <si>
-    <t>Kaimo gyventojas (Pelkė)</t>
-  </si>
-  <si>
-    <t>Villager (Taiga)</t>
-  </si>
-  <si>
-    <t>Kaimo gyventojas (Taiga)</t>
-  </si>
-  <si>
-    <t>Virtual Youtuber</t>
-  </si>
-  <si>
-    <t>Virtualus youtuberis</t>
-  </si>
-  <si>
-    <t>Vocaloid</t>
-  </si>
-  <si>
-    <t>Voltron</t>
-  </si>
-  <si>
-    <t>Voltronas</t>
-  </si>
-  <si>
-    <t>Wakfu</t>
-  </si>
-  <si>
-    <t>Walking Dead</t>
-  </si>
-  <si>
-    <t>Vaikščiojantys numirėliai</t>
-  </si>
-  <si>
-    <t>Wall-E</t>
-  </si>
-  <si>
-    <t>Wallace and Gromit</t>
-  </si>
-  <si>
-    <t>Volisas ir Gromitas</t>
-  </si>
-  <si>
-    <t>War of the Worlds</t>
-  </si>
-  <si>
-    <t>Pasaulių karas</t>
-  </si>
-  <si>
-    <t>Warcraft</t>
-  </si>
-  <si>
-    <t>Warframe</t>
-  </si>
-  <si>
-    <t>Warhammer</t>
-  </si>
-  <si>
-    <t>Warrior Cats</t>
-  </si>
-  <si>
-    <t>Kariaujančios katės</t>
-  </si>
-  <si>
-    <t>We Bear Bears</t>
-  </si>
-  <si>
-    <t>Mes nešame meškiukus</t>
-  </si>
-  <si>
-    <t>We Happy Few</t>
-  </si>
-  <si>
-    <t>Mes laimingi nedaugelis</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
-    <t>Orai</t>
-  </si>
-  <si>
-    <t>Welcome Home</t>
-  </si>
-  <si>
-    <t>Sveiki atvykę į namus</t>
-  </si>
-  <si>
-    <t>Who is this?</t>
-  </si>
-  <si>
-    <t>Kas tai?</t>
-  </si>
-  <si>
-    <t>Wild Update</t>
-  </si>
-  <si>
-    <t>Laukinis atnaujinimas</t>
-  </si>
-  <si>
-    <t>Wings of Fire</t>
-  </si>
-  <si>
-    <t>Ugnies sparnai</t>
-  </si>
-  <si>
-    <t>Winnie the Pooh</t>
-  </si>
-  <si>
-    <t>Meškiukas Pūkuotukas</t>
-  </si>
-  <si>
-    <t>Winter</t>
-  </si>
-  <si>
-    <t>Žiema</t>
-  </si>
-  <si>
-    <t>Witcher</t>
-  </si>
-  <si>
-    <t>Wonderful Wonder World</t>
-  </si>
-  <si>
-    <t>Nuostabus stebuklų pasaulis</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>Mediena</t>
-  </si>
-  <si>
-    <t>Wool</t>
-  </si>
-  <si>
-    <t>Vilna</t>
-  </si>
-  <si>
-    <t>Work Safety Helmet</t>
-  </si>
-  <si>
-    <t>Darbo saugos šalmas</t>
-  </si>
-  <si>
-    <t>Wreck It Ralph</t>
-  </si>
-  <si>
-    <t>Išardyti Ralfą (Wreck It Ralph)</t>
-  </si>
-  <si>
-    <t>Wybel</t>
-  </si>
-  <si>
-    <t>Wynncraft</t>
-  </si>
-  <si>
-    <t>X-Men</t>
-  </si>
-  <si>
-    <t>X-Menai</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles</t>
-  </si>
-  <si>
-    <t>"Xenoblade Chronicles</t>
-  </si>
-  <si>
-    <t>Yandere Simulator</t>
-  </si>
-  <si>
-    <t>Yandere simuliatorius</t>
-  </si>
-  <si>
-    <t>Yellow Submarine</t>
-  </si>
-  <si>
-    <t>Geltonasis povandeninis laivas</t>
-  </si>
-  <si>
-    <t>Yokai</t>
-  </si>
-  <si>
-    <t>Yooka Laylee</t>
-  </si>
-  <si>
-    <t>"Yooka Laylee</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>Jaunimas</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>"Youtube"</t>
-  </si>
-  <si>
-    <t>Yu-Gi-Oh</t>
-  </si>
-  <si>
-    <t>Yume Nikki</t>
-  </si>
-  <si>
-    <t>Zero no Tsukaima</t>
-  </si>
-  <si>
-    <t>Zero Wing</t>
-  </si>
-  <si>
-    <t>Nulinis sparnas</t>
-  </si>
-  <si>
-    <t>Zodiac Sign</t>
-  </si>
-  <si>
-    <t>Zodiako ženklas</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>Zombie (Vanilla)</t>
-  </si>
-  <si>
-    <t>Zombis (vanilė)</t>
-  </si>
-  <si>
-    <t>Zootopia</t>
-  </si>
-  <si>
-    <t>Zootopija</t>
   </si>
   <si>
     <t>Hypixel (Mutations) Tag</t>
@@ -6633,7 +6636,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1177"/>
+  <dimension ref="A1:B1178"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -16045,19 +16048,27 @@
         <v>2086</v>
       </c>
       <c r="B1176" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B1177" t="s">
         <v>2088</v>
       </c>
-      <c r="B1177" t="s">
+    </row>
+    <row r="1178" spans="1:2">
+      <c r="A1178" t="s">
         <v>2089</v>
       </c>
+      <c r="B1178" t="s">
+        <v>2090</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1177"/>
+  <autoFilter ref="A1:B1178"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2092">
   <si>
     <t>en</t>
   </si>
@@ -4295,6 +4295,9 @@
   </si>
   <si>
     <t>Atvirojo kodo objektai</t>
+  </si>
+  <si>
+    <t>Opus Magnum</t>
   </si>
   <si>
     <t>Orb</t>
@@ -6636,7 +6639,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1178"/>
+  <dimension ref="A1:B1179"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13032,68 +13035,68 @@
         <v>1427</v>
       </c>
       <c r="B799" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B800" t="s">
         <v>1429</v>
-      </c>
-      <c r="B800" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B801" t="s">
         <v>1431</v>
-      </c>
-      <c r="B801" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B802" t="s">
         <v>1433</v>
-      </c>
-      <c r="B802" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B803" t="s">
         <v>1435</v>
-      </c>
-      <c r="B803" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B804" t="s">
         <v>1437</v>
-      </c>
-      <c r="B804" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B805" t="s">
         <v>1439</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B806" t="s">
         <v>1441</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1442</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B807" t="s">
         <v>1443</v>
@@ -13112,36 +13115,36 @@
         <v>1445</v>
       </c>
       <c r="B809" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B810" t="s">
         <v>1447</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B811" t="s">
         <v>1449</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B812" t="s">
         <v>1451</v>
-      </c>
-      <c r="B812" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B813" t="s">
         <v>1453</v>
@@ -13152,20 +13155,20 @@
         <v>1454</v>
       </c>
       <c r="B814" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B815" t="s">
         <v>1456</v>
-      </c>
-      <c r="B815" t="s">
-        <v>1457</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B816" t="s">
         <v>1458</v>
@@ -13176,20 +13179,20 @@
         <v>1459</v>
       </c>
       <c r="B817" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B818" t="s">
         <v>1461</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B819" t="s">
         <v>1463</v>
@@ -13200,28 +13203,28 @@
         <v>1464</v>
       </c>
       <c r="B820" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B821" t="s">
         <v>1466</v>
-      </c>
-      <c r="B821" t="s">
-        <v>1467</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B822" t="s">
         <v>1468</v>
-      </c>
-      <c r="B822" t="s">
-        <v>1469</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B823" t="s">
         <v>1470</v>
@@ -13232,12 +13235,12 @@
         <v>1471</v>
       </c>
       <c r="B824" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B825" t="s">
         <v>1473</v>
@@ -13248,44 +13251,44 @@
         <v>1474</v>
       </c>
       <c r="B826" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B827" t="s">
         <v>1476</v>
-      </c>
-      <c r="B827" t="s">
-        <v>1477</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B828" t="s">
         <v>1478</v>
-      </c>
-      <c r="B828" t="s">
-        <v>1479</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B829" t="s">
         <v>1480</v>
-      </c>
-      <c r="B829" t="s">
-        <v>1481</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B830" t="s">
         <v>1482</v>
-      </c>
-      <c r="B830" t="s">
-        <v>1483</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B831" t="s">
         <v>1484</v>
@@ -13320,68 +13323,68 @@
         <v>1488</v>
       </c>
       <c r="B835" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B836" t="s">
         <v>1490</v>
-      </c>
-      <c r="B836" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B837" t="s">
         <v>1492</v>
-      </c>
-      <c r="B837" t="s">
-        <v>1493</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B838" t="s">
         <v>1494</v>
-      </c>
-      <c r="B838" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B839" t="s">
         <v>1496</v>
-      </c>
-      <c r="B839" t="s">
-        <v>1497</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B840" t="s">
         <v>1498</v>
-      </c>
-      <c r="B840" t="s">
-        <v>1499</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B841" t="s">
         <v>1500</v>
-      </c>
-      <c r="B841" t="s">
-        <v>1501</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B842" t="s">
         <v>1502</v>
-      </c>
-      <c r="B842" t="s">
-        <v>1503</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B843" t="s">
         <v>1504</v>
@@ -13408,108 +13411,108 @@
         <v>1507</v>
       </c>
       <c r="B846" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B847" t="s">
         <v>1509</v>
-      </c>
-      <c r="B847" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B848" t="s">
         <v>1511</v>
-      </c>
-      <c r="B848" t="s">
-        <v>1512</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B849" t="s">
         <v>1513</v>
-      </c>
-      <c r="B849" t="s">
-        <v>1514</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B850" t="s">
         <v>1515</v>
-      </c>
-      <c r="B850" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B851" t="s">
         <v>1517</v>
-      </c>
-      <c r="B851" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B852" t="s">
         <v>1519</v>
-      </c>
-      <c r="B852" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B853" t="s">
         <v>1521</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1522</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B854" t="s">
         <v>1523</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1524</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B855" t="s">
         <v>1525</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1526</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B856" t="s">
         <v>1527</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1528</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B857" t="s">
         <v>1529</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1530</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B858" t="s">
         <v>1531</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1532</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B859" t="s">
         <v>1533</v>
@@ -13528,12 +13531,12 @@
         <v>1535</v>
       </c>
       <c r="B861" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B862" t="s">
         <v>1537</v>
@@ -13544,12 +13547,12 @@
         <v>1538</v>
       </c>
       <c r="B863" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B864" t="s">
         <v>1540</v>
@@ -13560,108 +13563,108 @@
         <v>1541</v>
       </c>
       <c r="B865" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B866" t="s">
         <v>1543</v>
-      </c>
-      <c r="B866" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B867" t="s">
         <v>1545</v>
-      </c>
-      <c r="B867" t="s">
-        <v>1546</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B868" t="s">
         <v>1547</v>
-      </c>
-      <c r="B868" t="s">
-        <v>1548</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B869" t="s">
         <v>1549</v>
-      </c>
-      <c r="B869" t="s">
-        <v>1550</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B870" t="s">
         <v>1551</v>
-      </c>
-      <c r="B870" t="s">
-        <v>1552</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B871" t="s">
         <v>1553</v>
-      </c>
-      <c r="B871" t="s">
-        <v>1554</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B872" t="s">
         <v>1555</v>
-      </c>
-      <c r="B872" t="s">
-        <v>1556</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B873" t="s">
         <v>1557</v>
-      </c>
-      <c r="B873" t="s">
-        <v>1558</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B874" t="s">
         <v>1559</v>
-      </c>
-      <c r="B874" t="s">
-        <v>1560</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B875" t="s">
         <v>1561</v>
-      </c>
-      <c r="B875" t="s">
-        <v>1562</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B876" t="s">
         <v>1563</v>
-      </c>
-      <c r="B876" t="s">
-        <v>1564</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B877" t="s">
         <v>1565</v>
-      </c>
-      <c r="B877" t="s">
-        <v>1566</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B878" t="s">
         <v>1567</v>
@@ -13680,28 +13683,28 @@
         <v>1569</v>
       </c>
       <c r="B880" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B881" t="s">
         <v>1571</v>
-      </c>
-      <c r="B881" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B882" t="s">
         <v>1573</v>
-      </c>
-      <c r="B882" t="s">
-        <v>1574</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B883" t="s">
         <v>1575</v>
@@ -13712,20 +13715,20 @@
         <v>1576</v>
       </c>
       <c r="B884" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B885" t="s">
         <v>1578</v>
-      </c>
-      <c r="B885" t="s">
-        <v>1579</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="B886" t="s">
         <v>1580</v>
@@ -13736,12 +13739,12 @@
         <v>1581</v>
       </c>
       <c r="B887" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B888" t="s">
         <v>1583</v>
@@ -13752,12 +13755,12 @@
         <v>1584</v>
       </c>
       <c r="B889" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="B890" t="s">
         <v>1586</v>
@@ -13768,12 +13771,12 @@
         <v>1587</v>
       </c>
       <c r="B891" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B892" t="s">
         <v>1589</v>
@@ -13784,60 +13787,60 @@
         <v>1590</v>
       </c>
       <c r="B893" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B894" t="s">
         <v>1592</v>
-      </c>
-      <c r="B894" t="s">
-        <v>1593</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B895" t="s">
         <v>1594</v>
-      </c>
-      <c r="B895" t="s">
-        <v>1595</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B896" t="s">
         <v>1596</v>
-      </c>
-      <c r="B896" t="s">
-        <v>1597</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B897" t="s">
         <v>1598</v>
-      </c>
-      <c r="B897" t="s">
-        <v>1599</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B898" t="s">
         <v>1600</v>
-      </c>
-      <c r="B898" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B899" t="s">
         <v>1602</v>
-      </c>
-      <c r="B899" t="s">
-        <v>1603</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="B900" t="s">
         <v>1604</v>
@@ -13848,28 +13851,28 @@
         <v>1605</v>
       </c>
       <c r="B901" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B902" t="s">
         <v>1607</v>
-      </c>
-      <c r="B902" t="s">
-        <v>1608</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B903" t="s">
         <v>1609</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B904" t="s">
         <v>1611</v>
@@ -13880,12 +13883,12 @@
         <v>1612</v>
       </c>
       <c r="B905" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="B906" t="s">
         <v>1614</v>
@@ -13904,12 +13907,12 @@
         <v>1616</v>
       </c>
       <c r="B908" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B909" t="s">
         <v>1618</v>
@@ -13920,36 +13923,36 @@
         <v>1619</v>
       </c>
       <c r="B910" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B911" t="s">
         <v>1621</v>
-      </c>
-      <c r="B911" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B912" t="s">
         <v>1623</v>
-      </c>
-      <c r="B912" t="s">
-        <v>1624</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B913" t="s">
         <v>1625</v>
-      </c>
-      <c r="B913" t="s">
-        <v>1626</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="B914" t="s">
         <v>1627</v>
@@ -13976,44 +13979,44 @@
         <v>1630</v>
       </c>
       <c r="B917" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B918" t="s">
         <v>1632</v>
-      </c>
-      <c r="B918" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B919" t="s">
         <v>1634</v>
-      </c>
-      <c r="B919" t="s">
-        <v>1635</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B920" t="s">
         <v>1636</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1637</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B921" t="s">
         <v>1638</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="B922" t="s">
         <v>1640</v>
@@ -14032,36 +14035,36 @@
         <v>1642</v>
       </c>
       <c r="B924" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B925" t="s">
         <v>1644</v>
-      </c>
-      <c r="B925" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B926" t="s">
         <v>1646</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1647</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B927" t="s">
         <v>1648</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B928" t="s">
         <v>1650</v>
@@ -14072,12 +14075,12 @@
         <v>1651</v>
       </c>
       <c r="B929" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="B930" t="s">
         <v>1653</v>
@@ -14096,84 +14099,84 @@
         <v>1655</v>
       </c>
       <c r="B932" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B933" t="s">
         <v>1657</v>
-      </c>
-      <c r="B933" t="s">
-        <v>1658</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B934" t="s">
         <v>1659</v>
-      </c>
-      <c r="B934" t="s">
-        <v>1660</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B935" t="s">
         <v>1661</v>
-      </c>
-      <c r="B935" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B936" t="s">
         <v>1663</v>
-      </c>
-      <c r="B936" t="s">
-        <v>1664</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B937" t="s">
         <v>1665</v>
-      </c>
-      <c r="B937" t="s">
-        <v>1666</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B938" t="s">
         <v>1667</v>
-      </c>
-      <c r="B938" t="s">
-        <v>1668</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B939" t="s">
         <v>1669</v>
-      </c>
-      <c r="B939" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B940" t="s">
         <v>1671</v>
-      </c>
-      <c r="B940" t="s">
-        <v>1672</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B941" t="s">
         <v>1673</v>
-      </c>
-      <c r="B941" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="B942" t="s">
         <v>1675</v>
@@ -14192,20 +14195,20 @@
         <v>1677</v>
       </c>
       <c r="B944" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B945" t="s">
         <v>1679</v>
-      </c>
-      <c r="B945" t="s">
-        <v>1680</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="B946" t="s">
         <v>1681</v>
@@ -14216,12 +14219,12 @@
         <v>1682</v>
       </c>
       <c r="B947" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="B948" t="s">
         <v>1684</v>
@@ -14248,44 +14251,44 @@
         <v>1687</v>
       </c>
       <c r="B951" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B952" t="s">
         <v>1689</v>
-      </c>
-      <c r="B952" t="s">
-        <v>1690</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B953" t="s">
         <v>1691</v>
-      </c>
-      <c r="B953" t="s">
-        <v>1692</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B954" t="s">
         <v>1693</v>
-      </c>
-      <c r="B954" t="s">
-        <v>1694</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B955" t="s">
         <v>1695</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1696</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="B956" t="s">
         <v>1697</v>
@@ -14304,60 +14307,60 @@
         <v>1699</v>
       </c>
       <c r="B958" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B959" t="s">
         <v>1701</v>
-      </c>
-      <c r="B959" t="s">
-        <v>1702</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B960" t="s">
         <v>1703</v>
-      </c>
-      <c r="B960" t="s">
-        <v>1704</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B961" t="s">
         <v>1705</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1706</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B962" t="s">
         <v>1707</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B963" t="s">
         <v>1709</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B964" t="s">
         <v>1711</v>
-      </c>
-      <c r="B964" t="s">
-        <v>1712</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="B965" t="s">
         <v>1713</v>
@@ -14376,100 +14379,100 @@
         <v>1715</v>
       </c>
       <c r="B967" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B968" t="s">
         <v>1717</v>
-      </c>
-      <c r="B968" t="s">
-        <v>1718</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B969" t="s">
         <v>1719</v>
-      </c>
-      <c r="B969" t="s">
-        <v>1720</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B970" t="s">
         <v>1721</v>
-      </c>
-      <c r="B970" t="s">
-        <v>1722</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B971" t="s">
         <v>1723</v>
-      </c>
-      <c r="B971" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B972" t="s">
         <v>1725</v>
-      </c>
-      <c r="B972" t="s">
-        <v>1726</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B973" t="s">
         <v>1727</v>
-      </c>
-      <c r="B973" t="s">
-        <v>1728</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B974" t="s">
         <v>1729</v>
-      </c>
-      <c r="B974" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B975" t="s">
         <v>1731</v>
-      </c>
-      <c r="B975" t="s">
-        <v>1732</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B976" t="s">
         <v>1733</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1734</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B977" t="s">
         <v>1735</v>
-      </c>
-      <c r="B977" t="s">
-        <v>1736</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B978" t="s">
         <v>1737</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="B979" t="s">
         <v>1739</v>
@@ -14488,36 +14491,36 @@
         <v>1741</v>
       </c>
       <c r="B981" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B982" t="s">
         <v>1743</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1744</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B983" t="s">
         <v>1745</v>
-      </c>
-      <c r="B983" t="s">
-        <v>1746</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B984" t="s">
         <v>1747</v>
-      </c>
-      <c r="B984" t="s">
-        <v>1748</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="B985" t="s">
         <v>1749</v>
@@ -14528,12 +14531,12 @@
         <v>1750</v>
       </c>
       <c r="B986" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="B987" t="s">
         <v>1752</v>
@@ -14544,15 +14547,15 @@
         <v>1753</v>
       </c>
       <c r="B988" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B989" t="s">
         <v>1755</v>
-      </c>
-      <c r="B989" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="990" spans="1:2">
@@ -14560,28 +14563,28 @@
         <v>1756</v>
       </c>
       <c r="B990" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B991" t="s">
         <v>1758</v>
-      </c>
-      <c r="B991" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B992" t="s">
         <v>1760</v>
-      </c>
-      <c r="B992" t="s">
-        <v>1761</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="B993" t="s">
         <v>1762</v>
@@ -14592,20 +14595,20 @@
         <v>1763</v>
       </c>
       <c r="B994" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B995" t="s">
         <v>1765</v>
-      </c>
-      <c r="B995" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B996" t="s">
         <v>1767</v>
@@ -14616,60 +14619,60 @@
         <v>1768</v>
       </c>
       <c r="B997" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B998" t="s">
         <v>1770</v>
-      </c>
-      <c r="B998" t="s">
-        <v>1771</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B999" t="s">
         <v>1772</v>
-      </c>
-      <c r="B999" t="s">
-        <v>1773</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B1000" t="s">
         <v>1774</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B1001" t="s">
         <v>1776</v>
-      </c>
-      <c r="B1001" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B1002" t="s">
         <v>1778</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>1779</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1003" t="s">
         <v>1780</v>
-      </c>
-      <c r="B1003" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="B1004" t="s">
         <v>1782</v>
@@ -14688,20 +14691,20 @@
         <v>1784</v>
       </c>
       <c r="B1006" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B1007" t="s">
         <v>1786</v>
-      </c>
-      <c r="B1007" t="s">
-        <v>1787</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B1008" t="s">
         <v>1788</v>
@@ -14712,12 +14715,12 @@
         <v>1789</v>
       </c>
       <c r="B1009" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="B1010" t="s">
         <v>1791</v>
@@ -14736,36 +14739,36 @@
         <v>1793</v>
       </c>
       <c r="B1012" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B1013" t="s">
         <v>1795</v>
-      </c>
-      <c r="B1013" t="s">
-        <v>1796</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B1014" t="s">
         <v>1797</v>
-      </c>
-      <c r="B1014" t="s">
-        <v>1798</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1015" t="s">
         <v>1799</v>
-      </c>
-      <c r="B1015" t="s">
-        <v>1800</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="B1016" t="s">
         <v>1801</v>
@@ -14784,20 +14787,20 @@
         <v>1803</v>
       </c>
       <c r="B1018" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B1019" t="s">
         <v>1805</v>
-      </c>
-      <c r="B1019" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B1020" t="s">
         <v>1807</v>
@@ -14808,52 +14811,52 @@
         <v>1808</v>
       </c>
       <c r="B1021" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B1022" t="s">
         <v>1810</v>
-      </c>
-      <c r="B1022" t="s">
-        <v>1811</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B1023" t="s">
         <v>1812</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>1813</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B1024" t="s">
         <v>1814</v>
-      </c>
-      <c r="B1024" t="s">
-        <v>1815</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B1025" t="s">
         <v>1816</v>
-      </c>
-      <c r="B1025" t="s">
-        <v>1817</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B1026" t="s">
         <v>1818</v>
-      </c>
-      <c r="B1026" t="s">
-        <v>1819</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B1027" t="s">
         <v>1820</v>
@@ -14864,36 +14867,36 @@
         <v>1821</v>
       </c>
       <c r="B1028" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1029" t="s">
         <v>1823</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>1824</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B1030" t="s">
         <v>1825</v>
-      </c>
-      <c r="B1030" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1031" t="s">
         <v>1827</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>1828</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="B1032" t="s">
         <v>1829</v>
@@ -14904,12 +14907,12 @@
         <v>1830</v>
       </c>
       <c r="B1033" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="B1034" t="s">
         <v>1832</v>
@@ -14920,20 +14923,20 @@
         <v>1833</v>
       </c>
       <c r="B1035" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B1036" t="s">
         <v>1835</v>
-      </c>
-      <c r="B1036" t="s">
-        <v>1836</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="B1037" t="s">
         <v>1837</v>
@@ -14944,28 +14947,28 @@
         <v>1838</v>
       </c>
       <c r="B1038" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B1039" t="s">
         <v>1840</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>1841</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B1040" t="s">
         <v>1842</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>1843</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="B1041" t="s">
         <v>1844</v>
@@ -14976,148 +14979,148 @@
         <v>1845</v>
       </c>
       <c r="B1042" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B1043" t="s">
         <v>1847</v>
-      </c>
-      <c r="B1043" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1044" t="s">
         <v>1849</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B1045" t="s">
         <v>1851</v>
-      </c>
-      <c r="B1045" t="s">
-        <v>1852</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B1046" t="s">
         <v>1853</v>
-      </c>
-      <c r="B1046" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B1047" t="s">
         <v>1855</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B1048" t="s">
         <v>1857</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>1858</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B1049" t="s">
         <v>1859</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>1860</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B1050" t="s">
         <v>1861</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>1862</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1051" t="s">
         <v>1863</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>1864</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1052" t="s">
         <v>1865</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>1866</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B1053" t="s">
         <v>1867</v>
-      </c>
-      <c r="B1053" t="s">
-        <v>1868</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B1054" t="s">
         <v>1869</v>
-      </c>
-      <c r="B1054" t="s">
-        <v>1870</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B1055" t="s">
         <v>1871</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>1872</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1873</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>1874</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B1057" t="s">
         <v>1875</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>1876</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1058" t="s">
         <v>1877</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1878</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1879</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1880</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="B1060" t="s">
         <v>1881</v>
@@ -15128,76 +15131,76 @@
         <v>1882</v>
       </c>
       <c r="B1061" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B1062" t="s">
         <v>1884</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>1885</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B1063" t="s">
         <v>1886</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>1887</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B1064" t="s">
         <v>1888</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B1065" t="s">
         <v>1890</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>1891</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1892</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1893</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1894</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1895</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1896</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1897</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B1069" t="s">
         <v>1898</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>1899</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B1070" t="s">
         <v>1900</v>
@@ -15208,20 +15211,20 @@
         <v>1901</v>
       </c>
       <c r="B1071" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B1072" t="s">
         <v>1903</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>1904</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B1073" t="s">
         <v>1905</v>
@@ -15232,12 +15235,12 @@
         <v>1906</v>
       </c>
       <c r="B1074" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B1075" t="s">
         <v>1908</v>
@@ -15256,20 +15259,20 @@
         <v>1910</v>
       </c>
       <c r="B1077" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B1078" t="s">
         <v>1912</v>
-      </c>
-      <c r="B1078" t="s">
-        <v>1913</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B1079" t="s">
         <v>1914</v>
@@ -15280,20 +15283,20 @@
         <v>1915</v>
       </c>
       <c r="B1080" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B1081" t="s">
         <v>1917</v>
-      </c>
-      <c r="B1081" t="s">
-        <v>1918</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="B1082" t="s">
         <v>1919</v>
@@ -15304,76 +15307,76 @@
         <v>1920</v>
       </c>
       <c r="B1083" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B1084" t="s">
         <v>1922</v>
-      </c>
-      <c r="B1084" t="s">
-        <v>1923</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B1085" t="s">
         <v>1924</v>
-      </c>
-      <c r="B1085" t="s">
-        <v>1925</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B1086" t="s">
         <v>1926</v>
-      </c>
-      <c r="B1086" t="s">
-        <v>1927</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B1087" t="s">
         <v>1928</v>
-      </c>
-      <c r="B1087" t="s">
-        <v>1929</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B1088" t="s">
         <v>1930</v>
-      </c>
-      <c r="B1088" t="s">
-        <v>1931</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B1089" t="s">
         <v>1932</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>1933</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B1090" t="s">
         <v>1934</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>1935</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B1091" t="s">
         <v>1936</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>1937</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="B1092" t="s">
         <v>1938</v>
@@ -15384,76 +15387,76 @@
         <v>1939</v>
       </c>
       <c r="B1093" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1094" t="s">
         <v>1941</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>1942</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B1095" t="s">
         <v>1943</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>1944</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1096" t="s">
         <v>1945</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1097" t="s">
         <v>1947</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>1948</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B1098" t="s">
         <v>1949</v>
-      </c>
-      <c r="B1098" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B1099" t="s">
         <v>1951</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>1952</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B1100" t="s">
         <v>1953</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B1101" t="s">
         <v>1955</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>1956</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B1102" t="s">
         <v>1957</v>
@@ -15464,12 +15467,12 @@
         <v>1958</v>
       </c>
       <c r="B1103" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B1104" t="s">
         <v>1960</v>
@@ -15488,36 +15491,36 @@
         <v>1962</v>
       </c>
       <c r="B1106" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B1107" t="s">
         <v>1964</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>1965</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B1108" t="s">
         <v>1966</v>
-      </c>
-      <c r="B1108" t="s">
-        <v>1967</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B1109" t="s">
         <v>1968</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>1969</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B1110" t="s">
         <v>1970</v>
@@ -15528,12 +15531,12 @@
         <v>1971</v>
       </c>
       <c r="B1111" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B1112" t="s">
         <v>1973</v>
@@ -15544,156 +15547,156 @@
         <v>1974</v>
       </c>
       <c r="B1113" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B1114" t="s">
         <v>1976</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>1977</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B1115" t="s">
         <v>1978</v>
-      </c>
-      <c r="B1115" t="s">
-        <v>1979</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B1116" t="s">
         <v>1980</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>1981</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B1117" t="s">
         <v>1982</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>1983</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B1118" t="s">
         <v>1984</v>
-      </c>
-      <c r="B1118" t="s">
-        <v>1985</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B1119" t="s">
         <v>1986</v>
-      </c>
-      <c r="B1119" t="s">
-        <v>1987</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B1120" t="s">
         <v>1988</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>1989</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B1121" t="s">
         <v>1990</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>1991</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B1122" t="s">
         <v>1992</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>1993</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1994</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>1995</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1996</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1997</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1998</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1999</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1126" t="s">
         <v>2000</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>2001</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1127" t="s">
         <v>2002</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>2003</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1128" t="s">
         <v>2004</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>2005</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1129" t="s">
         <v>2006</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>2007</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1130" t="s">
         <v>2008</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>2009</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B1131" t="s">
         <v>2010</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>2011</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B1132" t="s">
         <v>2012</v>
@@ -15704,12 +15707,12 @@
         <v>2013</v>
       </c>
       <c r="B1133" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B1134" t="s">
         <v>2015</v>
@@ -15720,12 +15723,12 @@
         <v>2016</v>
       </c>
       <c r="B1135" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B1136" t="s">
         <v>2018</v>
@@ -15736,20 +15739,20 @@
         <v>2019</v>
       </c>
       <c r="B1137" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B1138" t="s">
         <v>2021</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>2022</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B1139" t="s">
         <v>2023</v>
@@ -15776,84 +15779,84 @@
         <v>2026</v>
       </c>
       <c r="B1142" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B1143" t="s">
         <v>2028</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>2029</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B1144" t="s">
         <v>2030</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>2031</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B1145" t="s">
         <v>2032</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>2033</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B1146" t="s">
         <v>2034</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>2035</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B1147" t="s">
         <v>2036</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>2037</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B1148" t="s">
         <v>2038</v>
-      </c>
-      <c r="B1148" t="s">
-        <v>2039</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B1149" t="s">
         <v>2040</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>2041</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B1150" t="s">
         <v>2042</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>2043</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B1151" t="s">
         <v>2044</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>2045</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B1152" t="s">
         <v>2046</v>
@@ -15864,44 +15867,44 @@
         <v>2047</v>
       </c>
       <c r="B1153" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B1154" t="s">
         <v>2049</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>2050</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B1155" t="s">
         <v>2051</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>2052</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B1156" t="s">
         <v>2053</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>2054</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B1157" t="s">
         <v>2055</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>2056</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="B1158" t="s">
         <v>2057</v>
@@ -15920,36 +15923,36 @@
         <v>2059</v>
       </c>
       <c r="B1160" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B1161" t="s">
         <v>2061</v>
-      </c>
-      <c r="B1161" t="s">
-        <v>2062</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1162" t="s">
         <v>2063</v>
-      </c>
-      <c r="B1162" t="s">
-        <v>2064</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B1163" t="s">
         <v>2065</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>2066</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="B1164" t="s">
         <v>2067</v>
@@ -15960,28 +15963,28 @@
         <v>2068</v>
       </c>
       <c r="B1165" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B1166" t="s">
         <v>2070</v>
-      </c>
-      <c r="B1166" t="s">
-        <v>2071</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B1167" t="s">
         <v>2072</v>
-      </c>
-      <c r="B1167" t="s">
-        <v>2073</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="B1168" t="s">
         <v>2074</v>
@@ -16008,20 +16011,20 @@
         <v>2077</v>
       </c>
       <c r="B1171" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B1172" t="s">
         <v>2079</v>
-      </c>
-      <c r="B1172" t="s">
-        <v>2080</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="B1173" t="s">
         <v>2081</v>
@@ -16032,20 +16035,20 @@
         <v>2082</v>
       </c>
       <c r="B1174" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B1175" t="s">
         <v>2084</v>
-      </c>
-      <c r="B1175" t="s">
-        <v>2085</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="B1176" t="s">
         <v>2086</v>
@@ -16056,19 +16059,27 @@
         <v>2087</v>
       </c>
       <c r="B1177" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B1178" t="s">
         <v>2089</v>
       </c>
-      <c r="B1178" t="s">
+    </row>
+    <row r="1179" spans="1:2">
+      <c r="A1179" t="s">
         <v>2090</v>
       </c>
+      <c r="B1179" t="s">
+        <v>2091</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1178"/>
+  <autoFilter ref="A1:B1179"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2094">
   <si>
     <t>en</t>
   </si>
@@ -878,6 +878,12 @@
   </si>
   <si>
     <t>Taurė</t>
+  </si>
+  <si>
+    <t>Chaos Cubed</t>
+  </si>
+  <si>
+    <t>Chaoso kubas</t>
   </si>
   <si>
     <t>Charlie and the Chocolate Factory</t>
@@ -6639,7 +6645,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1179"/>
+  <dimension ref="A1:B1180"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -8043,12 +8049,12 @@
         <v>311</v>
       </c>
       <c r="B175" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B176" t="s">
         <v>313</v>
@@ -8059,12 +8065,12 @@
         <v>314</v>
       </c>
       <c r="B177" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B178" t="s">
         <v>316</v>
@@ -8275,12 +8281,12 @@
         <v>367</v>
       </c>
       <c r="B204" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B205" t="s">
         <v>369</v>
@@ -8299,20 +8305,20 @@
         <v>372</v>
       </c>
       <c r="B207" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B208" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B209" t="s">
         <v>375</v>
@@ -8355,12 +8361,12 @@
         <v>384</v>
       </c>
       <c r="B214" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B215" t="s">
         <v>386</v>
@@ -8379,12 +8385,12 @@
         <v>389</v>
       </c>
       <c r="B217" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B218" t="s">
         <v>391</v>
@@ -8395,12 +8401,12 @@
         <v>392</v>
       </c>
       <c r="B219" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B220" t="s">
         <v>394</v>
@@ -8411,20 +8417,20 @@
         <v>395</v>
       </c>
       <c r="B221" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B222" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B223" t="s">
         <v>398</v>
@@ -8459,12 +8465,12 @@
         <v>405</v>
       </c>
       <c r="B227" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B228" t="s">
         <v>407</v>
@@ -8483,12 +8489,12 @@
         <v>410</v>
       </c>
       <c r="B230" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B231" t="s">
         <v>412</v>
@@ -8515,12 +8521,12 @@
         <v>417</v>
       </c>
       <c r="B234" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B235" t="s">
         <v>419</v>
@@ -8587,12 +8593,12 @@
         <v>434</v>
       </c>
       <c r="B243" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B244" t="s">
         <v>436</v>
@@ -8627,12 +8633,12 @@
         <v>443</v>
       </c>
       <c r="B248" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B249" t="s">
         <v>445</v>
@@ -8643,12 +8649,12 @@
         <v>446</v>
       </c>
       <c r="B250" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B251" t="s">
         <v>448</v>
@@ -8659,20 +8665,20 @@
         <v>449</v>
       </c>
       <c r="B252" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B253" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B254" t="s">
         <v>452</v>
@@ -8683,12 +8689,12 @@
         <v>453</v>
       </c>
       <c r="B255" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B256" t="s">
         <v>455</v>
@@ -8755,20 +8761,20 @@
         <v>470</v>
       </c>
       <c r="B264" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B265" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B266" t="s">
         <v>473</v>
@@ -8787,28 +8793,28 @@
         <v>476</v>
       </c>
       <c r="B268" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B269" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B270" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B271" t="s">
         <v>480</v>
@@ -8835,20 +8841,20 @@
         <v>485</v>
       </c>
       <c r="B274" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B275" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B276" t="s">
         <v>488</v>
@@ -8891,20 +8897,20 @@
         <v>497</v>
       </c>
       <c r="B281" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B282" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B283" t="s">
         <v>500</v>
@@ -8923,12 +8929,12 @@
         <v>503</v>
       </c>
       <c r="B285" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B286" t="s">
         <v>505</v>
@@ -8955,12 +8961,12 @@
         <v>510</v>
       </c>
       <c r="B289" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B290" t="s">
         <v>512</v>
@@ -8995,20 +9001,20 @@
         <v>519</v>
       </c>
       <c r="B294" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B295" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B296" t="s">
         <v>522</v>
@@ -9059,12 +9065,12 @@
         <v>533</v>
       </c>
       <c r="B302" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B303" t="s">
         <v>535</v>
@@ -9083,12 +9089,12 @@
         <v>538</v>
       </c>
       <c r="B305" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B306" t="s">
         <v>540</v>
@@ -9107,20 +9113,20 @@
         <v>543</v>
       </c>
       <c r="B308" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B309" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B310" t="s">
         <v>546</v>
@@ -9139,20 +9145,20 @@
         <v>549</v>
       </c>
       <c r="B312" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B313" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B314" t="s">
         <v>552</v>
@@ -9187,12 +9193,12 @@
         <v>559</v>
       </c>
       <c r="B318" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B319" t="s">
         <v>561</v>
@@ -9203,12 +9209,12 @@
         <v>562</v>
       </c>
       <c r="B320" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B321" t="s">
         <v>564</v>
@@ -9235,12 +9241,12 @@
         <v>569</v>
       </c>
       <c r="B324" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B325" t="s">
         <v>571</v>
@@ -9283,12 +9289,12 @@
         <v>580</v>
       </c>
       <c r="B330" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B331" t="s">
         <v>582</v>
@@ -9355,12 +9361,12 @@
         <v>597</v>
       </c>
       <c r="B339" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B340" t="s">
         <v>599</v>
@@ -10091,28 +10097,28 @@
         <v>780</v>
       </c>
       <c r="B431" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B432" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B433" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B434" t="s">
         <v>784</v>
@@ -10211,12 +10217,12 @@
         <v>807</v>
       </c>
       <c r="B446" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B447" t="s">
         <v>809</v>
@@ -10227,12 +10233,12 @@
         <v>810</v>
       </c>
       <c r="B448" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B449" t="s">
         <v>812</v>
@@ -10347,12 +10353,12 @@
         <v>839</v>
       </c>
       <c r="B463" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B464" t="s">
         <v>841</v>
@@ -10363,20 +10369,20 @@
         <v>842</v>
       </c>
       <c r="B465" t="s">
-        <v>558</v>
+        <v>843</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B466" t="s">
-        <v>843</v>
+        <v>560</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B467" t="s">
         <v>845</v>
@@ -10387,12 +10393,12 @@
         <v>846</v>
       </c>
       <c r="B468" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B469" t="s">
         <v>848</v>
@@ -10411,23 +10417,23 @@
         <v>851</v>
       </c>
       <c r="B471" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B472" t="s">
-        <v>558</v>
+        <v>853</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B473" t="s">
-        <v>854</v>
+        <v>560</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -10435,12 +10441,12 @@
         <v>855</v>
       </c>
       <c r="B474" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B475" t="s">
         <v>857</v>
@@ -10491,20 +10497,20 @@
         <v>868</v>
       </c>
       <c r="B481" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B482" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B483" t="s">
         <v>871</v>
@@ -10515,12 +10521,12 @@
         <v>872</v>
       </c>
       <c r="B484" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B485" t="s">
         <v>874</v>
@@ -10531,28 +10537,28 @@
         <v>875</v>
       </c>
       <c r="B486" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B487" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B488" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B489" t="s">
         <v>879</v>
@@ -10739,12 +10745,12 @@
         <v>924</v>
       </c>
       <c r="B512" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B513" t="s">
         <v>926</v>
@@ -10891,12 +10897,12 @@
         <v>961</v>
       </c>
       <c r="B531" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B532" t="s">
         <v>963</v>
@@ -10915,20 +10921,20 @@
         <v>966</v>
       </c>
       <c r="B534" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B535" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B536" t="s">
         <v>969</v>
@@ -10947,28 +10953,28 @@
         <v>972</v>
       </c>
       <c r="B538" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B539" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B540" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B541" t="s">
         <v>976</v>
@@ -11003,20 +11009,20 @@
         <v>983</v>
       </c>
       <c r="B545" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B546" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B547" t="s">
         <v>986</v>
@@ -11027,12 +11033,12 @@
         <v>987</v>
       </c>
       <c r="B548" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B549" t="s">
         <v>989</v>
@@ -11043,12 +11049,12 @@
         <v>990</v>
       </c>
       <c r="B550" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B551" t="s">
         <v>992</v>
@@ -11147,12 +11153,12 @@
         <v>1015</v>
       </c>
       <c r="B563" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B564" t="s">
         <v>1017</v>
@@ -11179,12 +11185,12 @@
         <v>1022</v>
       </c>
       <c r="B567" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B568" t="s">
         <v>1024</v>
@@ -11235,12 +11241,12 @@
         <v>1035</v>
       </c>
       <c r="B574" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B575" t="s">
         <v>1037</v>
@@ -11251,28 +11257,28 @@
         <v>1038</v>
       </c>
       <c r="B576" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B577" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B578" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B579" t="s">
         <v>1042</v>
@@ -11387,12 +11393,12 @@
         <v>1069</v>
       </c>
       <c r="B593" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B594" t="s">
         <v>1071</v>
@@ -11459,28 +11465,28 @@
         <v>1086</v>
       </c>
       <c r="B602" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B603" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B604" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B605" t="s">
         <v>1090</v>
@@ -11611,12 +11617,12 @@
         <v>1121</v>
       </c>
       <c r="B621" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B622" t="s">
         <v>1123</v>
@@ -11635,12 +11641,12 @@
         <v>1126</v>
       </c>
       <c r="B624" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B625" t="s">
         <v>1128</v>
@@ -11675,12 +11681,12 @@
         <v>1135</v>
       </c>
       <c r="B629" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B630" t="s">
         <v>1137</v>
@@ -11691,12 +11697,12 @@
         <v>1138</v>
       </c>
       <c r="B631" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B632" t="s">
         <v>1140</v>
@@ -11715,52 +11721,52 @@
         <v>1143</v>
       </c>
       <c r="B634" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B635" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B636" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B637" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B638" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B639" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B640" t="s">
         <v>1150</v>
@@ -11771,36 +11777,36 @@
         <v>1151</v>
       </c>
       <c r="B641" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B642" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B643" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B644" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B645" t="s">
         <v>1156</v>
@@ -11835,28 +11841,28 @@
         <v>1163</v>
       </c>
       <c r="B649" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B650" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B651" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B652" t="s">
         <v>1167</v>
@@ -11867,12 +11873,12 @@
         <v>1168</v>
       </c>
       <c r="B653" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B654" t="s">
         <v>1170</v>
@@ -12067,12 +12073,12 @@
         <v>1217</v>
       </c>
       <c r="B678" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B679" t="s">
         <v>1219</v>
@@ -12099,20 +12105,20 @@
         <v>1224</v>
       </c>
       <c r="B682" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B683" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B684" t="s">
         <v>1227</v>
@@ -12243,12 +12249,12 @@
         <v>1258</v>
       </c>
       <c r="B700" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B701" t="s">
         <v>1260</v>
@@ -12259,20 +12265,20 @@
         <v>1261</v>
       </c>
       <c r="B702" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B703" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B704" t="s">
         <v>1264</v>
@@ -12283,28 +12289,28 @@
         <v>1265</v>
       </c>
       <c r="B705" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B706" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B707" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B708" t="s">
         <v>1269</v>
@@ -12323,20 +12329,20 @@
         <v>1272</v>
       </c>
       <c r="B710" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B711" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B712" t="s">
         <v>1275</v>
@@ -12435,20 +12441,20 @@
         <v>1298</v>
       </c>
       <c r="B724" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B725" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B726" t="s">
         <v>1301</v>
@@ -12491,12 +12497,12 @@
         <v>1310</v>
       </c>
       <c r="B731" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B732" t="s">
         <v>1312</v>
@@ -12547,12 +12553,12 @@
         <v>1323</v>
       </c>
       <c r="B738" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B739" t="s">
         <v>1325</v>
@@ -12579,20 +12585,20 @@
         <v>1330</v>
       </c>
       <c r="B742" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B743" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B744" t="s">
         <v>1333</v>
@@ -12611,20 +12617,20 @@
         <v>1336</v>
       </c>
       <c r="B746" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B747" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B748" t="s">
         <v>1339</v>
@@ -12731,28 +12737,28 @@
         <v>1364</v>
       </c>
       <c r="B761" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="762" spans="1:2">
       <c r="A762" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B762" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B763" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B764" t="s">
         <v>1368</v>
@@ -12795,12 +12801,12 @@
         <v>1377</v>
       </c>
       <c r="B769" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B770" t="s">
         <v>1379</v>
@@ -12907,28 +12913,28 @@
         <v>1404</v>
       </c>
       <c r="B783" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B784" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B785" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B786" t="s">
         <v>1408</v>
@@ -12947,12 +12953,12 @@
         <v>1411</v>
       </c>
       <c r="B788" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B789" t="s">
         <v>1413</v>
@@ -12971,12 +12977,12 @@
         <v>1416</v>
       </c>
       <c r="B791" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B792" t="s">
         <v>1418</v>
@@ -12995,28 +13001,28 @@
         <v>1421</v>
       </c>
       <c r="B794" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B795" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B796" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B797" t="s">
         <v>1425</v>
@@ -13027,20 +13033,20 @@
         <v>1426</v>
       </c>
       <c r="B798" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B799" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B800" t="s">
         <v>1429</v>
@@ -13107,20 +13113,20 @@
         <v>1444</v>
       </c>
       <c r="B808" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B809" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B810" t="s">
         <v>1447</v>
@@ -13155,12 +13161,12 @@
         <v>1454</v>
       </c>
       <c r="B814" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B815" t="s">
         <v>1456</v>
@@ -13179,12 +13185,12 @@
         <v>1459</v>
       </c>
       <c r="B817" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B818" t="s">
         <v>1461</v>
@@ -13203,12 +13209,12 @@
         <v>1464</v>
       </c>
       <c r="B820" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B821" t="s">
         <v>1466</v>
@@ -13235,12 +13241,12 @@
         <v>1471</v>
       </c>
       <c r="B824" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B825" t="s">
         <v>1473</v>
@@ -13251,12 +13257,12 @@
         <v>1474</v>
       </c>
       <c r="B826" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B827" t="s">
         <v>1476</v>
@@ -13299,36 +13305,36 @@
         <v>1485</v>
       </c>
       <c r="B832" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B833" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B834" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B835" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B836" t="s">
         <v>1490</v>
@@ -13395,28 +13401,28 @@
         <v>1505</v>
       </c>
       <c r="B844" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B845" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B846" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B847" t="s">
         <v>1509</v>
@@ -13523,20 +13529,20 @@
         <v>1534</v>
       </c>
       <c r="B860" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B861" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B862" t="s">
         <v>1537</v>
@@ -13547,12 +13553,12 @@
         <v>1538</v>
       </c>
       <c r="B863" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B864" t="s">
         <v>1540</v>
@@ -13563,12 +13569,12 @@
         <v>1541</v>
       </c>
       <c r="B865" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B866" t="s">
         <v>1543</v>
@@ -13675,20 +13681,20 @@
         <v>1568</v>
       </c>
       <c r="B879" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B880" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B881" t="s">
         <v>1571</v>
@@ -13715,12 +13721,12 @@
         <v>1576</v>
       </c>
       <c r="B884" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B885" t="s">
         <v>1578</v>
@@ -13739,12 +13745,12 @@
         <v>1581</v>
       </c>
       <c r="B887" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B888" t="s">
         <v>1583</v>
@@ -13755,12 +13761,12 @@
         <v>1584</v>
       </c>
       <c r="B889" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B890" t="s">
         <v>1586</v>
@@ -13771,12 +13777,12 @@
         <v>1587</v>
       </c>
       <c r="B891" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B892" t="s">
         <v>1589</v>
@@ -13787,12 +13793,12 @@
         <v>1590</v>
       </c>
       <c r="B893" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B894" t="s">
         <v>1592</v>
@@ -13851,12 +13857,12 @@
         <v>1605</v>
       </c>
       <c r="B901" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B902" t="s">
         <v>1607</v>
@@ -13883,12 +13889,12 @@
         <v>1612</v>
       </c>
       <c r="B905" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B906" t="s">
         <v>1614</v>
@@ -13899,20 +13905,20 @@
         <v>1615</v>
       </c>
       <c r="B907" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B908" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B909" t="s">
         <v>1618</v>
@@ -13923,12 +13929,12 @@
         <v>1619</v>
       </c>
       <c r="B910" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B911" t="s">
         <v>1621</v>
@@ -13963,28 +13969,28 @@
         <v>1628</v>
       </c>
       <c r="B915" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B916" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B917" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B918" t="s">
         <v>1632</v>
@@ -14027,20 +14033,20 @@
         <v>1641</v>
       </c>
       <c r="B923" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B924" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B925" t="s">
         <v>1644</v>
@@ -14075,12 +14081,12 @@
         <v>1651</v>
       </c>
       <c r="B929" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B930" t="s">
         <v>1653</v>
@@ -14091,20 +14097,20 @@
         <v>1654</v>
       </c>
       <c r="B931" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B932" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B933" t="s">
         <v>1657</v>
@@ -14187,20 +14193,20 @@
         <v>1676</v>
       </c>
       <c r="B943" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B944" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B945" t="s">
         <v>1679</v>
@@ -14219,12 +14225,12 @@
         <v>1682</v>
       </c>
       <c r="B947" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B948" t="s">
         <v>1684</v>
@@ -14235,28 +14241,28 @@
         <v>1685</v>
       </c>
       <c r="B949" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B950" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B951" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B952" t="s">
         <v>1689</v>
@@ -14299,20 +14305,20 @@
         <v>1698</v>
       </c>
       <c r="B957" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B958" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B959" t="s">
         <v>1701</v>
@@ -14371,20 +14377,20 @@
         <v>1714</v>
       </c>
       <c r="B966" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B967" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B968" t="s">
         <v>1717</v>
@@ -14483,20 +14489,20 @@
         <v>1740</v>
       </c>
       <c r="B980" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B981" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B982" t="s">
         <v>1743</v>
@@ -14531,12 +14537,12 @@
         <v>1750</v>
       </c>
       <c r="B986" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B987" t="s">
         <v>1752</v>
@@ -14547,12 +14553,12 @@
         <v>1753</v>
       </c>
       <c r="B988" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B989" t="s">
         <v>1755</v>
@@ -14563,15 +14569,15 @@
         <v>1756</v>
       </c>
       <c r="B990" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B991" t="s">
         <v>1757</v>
-      </c>
-      <c r="B991" t="s">
-        <v>1758</v>
       </c>
     </row>
     <row r="992" spans="1:2">
@@ -14595,12 +14601,12 @@
         <v>1763</v>
       </c>
       <c r="B994" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B995" t="s">
         <v>1765</v>
@@ -14619,12 +14625,12 @@
         <v>1768</v>
       </c>
       <c r="B997" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B998" t="s">
         <v>1770</v>
@@ -14683,20 +14689,20 @@
         <v>1783</v>
       </c>
       <c r="B1005" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B1006" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B1007" t="s">
         <v>1786</v>
@@ -14715,12 +14721,12 @@
         <v>1789</v>
       </c>
       <c r="B1009" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B1010" t="s">
         <v>1791</v>
@@ -14731,20 +14737,20 @@
         <v>1792</v>
       </c>
       <c r="B1011" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1012" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B1013" t="s">
         <v>1795</v>
@@ -14779,20 +14785,20 @@
         <v>1802</v>
       </c>
       <c r="B1017" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B1018" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B1019" t="s">
         <v>1805</v>
@@ -14811,12 +14817,12 @@
         <v>1808</v>
       </c>
       <c r="B1021" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1022" t="s">
         <v>1810</v>
@@ -14867,12 +14873,12 @@
         <v>1821</v>
       </c>
       <c r="B1028" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1029" t="s">
         <v>1823</v>
@@ -14907,12 +14913,12 @@
         <v>1830</v>
       </c>
       <c r="B1033" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1034" t="s">
         <v>1832</v>
@@ -14923,12 +14929,12 @@
         <v>1833</v>
       </c>
       <c r="B1035" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1036" t="s">
         <v>1835</v>
@@ -14947,12 +14953,12 @@
         <v>1838</v>
       </c>
       <c r="B1038" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1039" t="s">
         <v>1840</v>
@@ -14979,12 +14985,12 @@
         <v>1845</v>
       </c>
       <c r="B1042" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B1043" t="s">
         <v>1847</v>
@@ -15131,12 +15137,12 @@
         <v>1882</v>
       </c>
       <c r="B1061" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B1062" t="s">
         <v>1884</v>
@@ -15211,12 +15217,12 @@
         <v>1901</v>
       </c>
       <c r="B1071" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B1072" t="s">
         <v>1903</v>
@@ -15235,12 +15241,12 @@
         <v>1906</v>
       </c>
       <c r="B1074" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1075" t="s">
         <v>1908</v>
@@ -15251,20 +15257,20 @@
         <v>1909</v>
       </c>
       <c r="B1076" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B1077" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B1078" t="s">
         <v>1912</v>
@@ -15283,12 +15289,12 @@
         <v>1915</v>
       </c>
       <c r="B1080" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B1081" t="s">
         <v>1917</v>
@@ -15307,12 +15313,12 @@
         <v>1920</v>
       </c>
       <c r="B1083" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1084" t="s">
         <v>1922</v>
@@ -15387,12 +15393,12 @@
         <v>1939</v>
       </c>
       <c r="B1093" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B1094" t="s">
         <v>1941</v>
@@ -15467,12 +15473,12 @@
         <v>1958</v>
       </c>
       <c r="B1103" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="B1104" t="s">
         <v>1960</v>
@@ -15483,20 +15489,20 @@
         <v>1961</v>
       </c>
       <c r="B1105" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B1106" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B1107" t="s">
         <v>1964</v>
@@ -15531,12 +15537,12 @@
         <v>1971</v>
       </c>
       <c r="B1111" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="B1112" t="s">
         <v>1973</v>
@@ -15547,12 +15553,12 @@
         <v>1974</v>
       </c>
       <c r="B1113" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1114" t="s">
         <v>1976</v>
@@ -15707,12 +15713,12 @@
         <v>2013</v>
       </c>
       <c r="B1133" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1134" t="s">
         <v>2015</v>
@@ -15723,12 +15729,12 @@
         <v>2016</v>
       </c>
       <c r="B1135" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B1136" t="s">
         <v>2018</v>
@@ -15739,12 +15745,12 @@
         <v>2019</v>
       </c>
       <c r="B1137" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B1138" t="s">
         <v>2021</v>
@@ -15763,28 +15769,28 @@
         <v>2024</v>
       </c>
       <c r="B1140" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B1141" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B1142" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B1143" t="s">
         <v>2028</v>
@@ -15867,12 +15873,12 @@
         <v>2047</v>
       </c>
       <c r="B1153" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B1154" t="s">
         <v>2049</v>
@@ -15915,20 +15921,20 @@
         <v>2058</v>
       </c>
       <c r="B1159" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="B1160" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="B1161" t="s">
         <v>2061</v>
@@ -15963,12 +15969,12 @@
         <v>2068</v>
       </c>
       <c r="B1165" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="B1166" t="s">
         <v>2070</v>
@@ -15995,28 +16001,28 @@
         <v>2075</v>
       </c>
       <c r="B1169" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="B1170" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="B1171" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="B1172" t="s">
         <v>2079</v>
@@ -16035,12 +16041,12 @@
         <v>2082</v>
       </c>
       <c r="B1174" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="B1175" t="s">
         <v>2084</v>
@@ -16059,12 +16065,12 @@
         <v>2087</v>
       </c>
       <c r="B1177" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="B1178" t="s">
         <v>2089</v>
@@ -16078,8 +16084,16 @@
         <v>2091</v>
       </c>
     </row>
+    <row r="1180" spans="1:2">
+      <c r="A1180" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>2093</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1179"/>
+  <autoFilter ref="A1:B1180"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2096">
   <si>
     <t>en</t>
   </si>
@@ -4637,6 +4637,12 @@
   </si>
   <si>
     <t>Pop komanda "Epic</t>
+  </si>
+  <si>
+    <t>Popee the Performer</t>
+  </si>
+  <si>
+    <t>Atlikėjas Popee</t>
   </si>
   <si>
     <t>POPGOES</t>
@@ -6645,7 +6651,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1180"/>
+  <dimension ref="A1:B1181"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13561,12 +13567,12 @@
         <v>1540</v>
       </c>
       <c r="B864" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B865" t="s">
         <v>1542</v>
@@ -13577,12 +13583,12 @@
         <v>1543</v>
       </c>
       <c r="B866" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B867" t="s">
         <v>1545</v>
@@ -13689,20 +13695,20 @@
         <v>1570</v>
       </c>
       <c r="B880" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B881" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B882" t="s">
         <v>1573</v>
@@ -13729,12 +13735,12 @@
         <v>1578</v>
       </c>
       <c r="B885" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B886" t="s">
         <v>1580</v>
@@ -13753,12 +13759,12 @@
         <v>1583</v>
       </c>
       <c r="B888" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B889" t="s">
         <v>1585</v>
@@ -13769,12 +13775,12 @@
         <v>1586</v>
       </c>
       <c r="B890" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B891" t="s">
         <v>1588</v>
@@ -13785,12 +13791,12 @@
         <v>1589</v>
       </c>
       <c r="B892" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B893" t="s">
         <v>1591</v>
@@ -13801,12 +13807,12 @@
         <v>1592</v>
       </c>
       <c r="B894" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B895" t="s">
         <v>1594</v>
@@ -13865,12 +13871,12 @@
         <v>1607</v>
       </c>
       <c r="B902" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B903" t="s">
         <v>1609</v>
@@ -13897,12 +13903,12 @@
         <v>1614</v>
       </c>
       <c r="B906" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B907" t="s">
         <v>1616</v>
@@ -13913,20 +13919,20 @@
         <v>1617</v>
       </c>
       <c r="B908" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B909" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B910" t="s">
         <v>1620</v>
@@ -13937,12 +13943,12 @@
         <v>1621</v>
       </c>
       <c r="B911" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B912" t="s">
         <v>1623</v>
@@ -13977,28 +13983,28 @@
         <v>1630</v>
       </c>
       <c r="B916" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B917" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B918" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B919" t="s">
         <v>1634</v>
@@ -14041,20 +14047,20 @@
         <v>1643</v>
       </c>
       <c r="B924" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B925" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B926" t="s">
         <v>1646</v>
@@ -14089,12 +14095,12 @@
         <v>1653</v>
       </c>
       <c r="B930" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B931" t="s">
         <v>1655</v>
@@ -14105,20 +14111,20 @@
         <v>1656</v>
       </c>
       <c r="B932" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B933" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B934" t="s">
         <v>1659</v>
@@ -14201,20 +14207,20 @@
         <v>1678</v>
       </c>
       <c r="B944" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B945" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B946" t="s">
         <v>1681</v>
@@ -14233,12 +14239,12 @@
         <v>1684</v>
       </c>
       <c r="B948" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B949" t="s">
         <v>1686</v>
@@ -14249,28 +14255,28 @@
         <v>1687</v>
       </c>
       <c r="B950" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B951" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B952" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B953" t="s">
         <v>1691</v>
@@ -14313,20 +14319,20 @@
         <v>1700</v>
       </c>
       <c r="B958" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B959" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B960" t="s">
         <v>1703</v>
@@ -14385,20 +14391,20 @@
         <v>1716</v>
       </c>
       <c r="B967" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B968" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B969" t="s">
         <v>1719</v>
@@ -14497,20 +14503,20 @@
         <v>1742</v>
       </c>
       <c r="B981" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B982" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B983" t="s">
         <v>1745</v>
@@ -14545,12 +14551,12 @@
         <v>1752</v>
       </c>
       <c r="B987" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B988" t="s">
         <v>1754</v>
@@ -14561,12 +14567,12 @@
         <v>1755</v>
       </c>
       <c r="B989" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B990" t="s">
         <v>1757</v>
@@ -14577,15 +14583,15 @@
         <v>1758</v>
       </c>
       <c r="B991" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B992" t="s">
         <v>1759</v>
-      </c>
-      <c r="B992" t="s">
-        <v>1760</v>
       </c>
     </row>
     <row r="993" spans="1:2">
@@ -14609,12 +14615,12 @@
         <v>1765</v>
       </c>
       <c r="B995" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B996" t="s">
         <v>1767</v>
@@ -14633,12 +14639,12 @@
         <v>1770</v>
       </c>
       <c r="B998" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B999" t="s">
         <v>1772</v>
@@ -14697,20 +14703,20 @@
         <v>1785</v>
       </c>
       <c r="B1006" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B1007" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B1008" t="s">
         <v>1788</v>
@@ -14729,12 +14735,12 @@
         <v>1791</v>
       </c>
       <c r="B1010" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1011" t="s">
         <v>1793</v>
@@ -14745,20 +14751,20 @@
         <v>1794</v>
       </c>
       <c r="B1012" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B1013" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1014" t="s">
         <v>1797</v>
@@ -14793,20 +14799,20 @@
         <v>1804</v>
       </c>
       <c r="B1018" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B1019" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B1020" t="s">
         <v>1807</v>
@@ -14825,12 +14831,12 @@
         <v>1810</v>
       </c>
       <c r="B1022" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1023" t="s">
         <v>1812</v>
@@ -14881,12 +14887,12 @@
         <v>1823</v>
       </c>
       <c r="B1029" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1030" t="s">
         <v>1825</v>
@@ -14921,12 +14927,12 @@
         <v>1832</v>
       </c>
       <c r="B1034" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1035" t="s">
         <v>1834</v>
@@ -14937,12 +14943,12 @@
         <v>1835</v>
       </c>
       <c r="B1036" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1037" t="s">
         <v>1837</v>
@@ -14961,12 +14967,12 @@
         <v>1840</v>
       </c>
       <c r="B1039" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1040" t="s">
         <v>1842</v>
@@ -14993,12 +14999,12 @@
         <v>1847</v>
       </c>
       <c r="B1043" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B1044" t="s">
         <v>1849</v>
@@ -15145,12 +15151,12 @@
         <v>1884</v>
       </c>
       <c r="B1062" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="B1063" t="s">
         <v>1886</v>
@@ -15225,12 +15231,12 @@
         <v>1903</v>
       </c>
       <c r="B1072" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1073" t="s">
         <v>1905</v>
@@ -15249,12 +15255,12 @@
         <v>1908</v>
       </c>
       <c r="B1075" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B1076" t="s">
         <v>1910</v>
@@ -15265,20 +15271,20 @@
         <v>1911</v>
       </c>
       <c r="B1077" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B1078" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1079" t="s">
         <v>1914</v>
@@ -15297,12 +15303,12 @@
         <v>1917</v>
       </c>
       <c r="B1081" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B1082" t="s">
         <v>1919</v>
@@ -15321,12 +15327,12 @@
         <v>1922</v>
       </c>
       <c r="B1084" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1085" t="s">
         <v>1924</v>
@@ -15401,12 +15407,12 @@
         <v>1941</v>
       </c>
       <c r="B1094" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B1095" t="s">
         <v>1943</v>
@@ -15481,12 +15487,12 @@
         <v>1960</v>
       </c>
       <c r="B1104" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="B1105" t="s">
         <v>1962</v>
@@ -15497,20 +15503,20 @@
         <v>1963</v>
       </c>
       <c r="B1106" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="B1107" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B1108" t="s">
         <v>1966</v>
@@ -15545,12 +15551,12 @@
         <v>1973</v>
       </c>
       <c r="B1112" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1113" t="s">
         <v>1975</v>
@@ -15561,12 +15567,12 @@
         <v>1976</v>
       </c>
       <c r="B1114" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B1115" t="s">
         <v>1978</v>
@@ -15721,12 +15727,12 @@
         <v>2015</v>
       </c>
       <c r="B1134" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B1135" t="s">
         <v>2017</v>
@@ -15737,12 +15743,12 @@
         <v>2018</v>
       </c>
       <c r="B1136" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B1137" t="s">
         <v>2020</v>
@@ -15753,12 +15759,12 @@
         <v>2021</v>
       </c>
       <c r="B1138" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B1139" t="s">
         <v>2023</v>
@@ -15777,28 +15783,28 @@
         <v>2026</v>
       </c>
       <c r="B1141" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B1142" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B1143" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B1144" t="s">
         <v>2030</v>
@@ -15881,12 +15887,12 @@
         <v>2049</v>
       </c>
       <c r="B1154" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="B1155" t="s">
         <v>2051</v>
@@ -15929,20 +15935,20 @@
         <v>2060</v>
       </c>
       <c r="B1160" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="B1161" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="B1162" t="s">
         <v>2063</v>
@@ -15977,12 +15983,12 @@
         <v>2070</v>
       </c>
       <c r="B1166" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="B1167" t="s">
         <v>2072</v>
@@ -16009,28 +16015,28 @@
         <v>2077</v>
       </c>
       <c r="B1170" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="B1171" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="B1172" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="B1173" t="s">
         <v>2081</v>
@@ -16049,12 +16055,12 @@
         <v>2084</v>
       </c>
       <c r="B1175" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="B1176" t="s">
         <v>2086</v>
@@ -16073,12 +16079,12 @@
         <v>2089</v>
       </c>
       <c r="B1178" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="B1179" t="s">
         <v>2091</v>
@@ -16092,8 +16098,16 @@
         <v>2093</v>
       </c>
     </row>
+    <row r="1181" spans="1:2">
+      <c r="A1181" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>2095</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1180"/>
+  <autoFilter ref="A1:B1181"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2098">
   <si>
     <t>en</t>
   </si>
@@ -5759,6 +5759,12 @@
   </si>
   <si>
     <t>Tinker's Construct</t>
+  </si>
+  <si>
+    <t>Tiny Takeover</t>
+  </si>
+  <si>
+    <t>Mažytis perėmimas</t>
   </si>
   <si>
     <t>Titanfall</t>
@@ -6651,7 +6657,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1181"/>
+  <dimension ref="A1:B1182"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15287,12 +15293,12 @@
         <v>1914</v>
       </c>
       <c r="B1079" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B1080" t="s">
         <v>1916</v>
@@ -15311,12 +15317,12 @@
         <v>1919</v>
       </c>
       <c r="B1082" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B1083" t="s">
         <v>1921</v>
@@ -15335,12 +15341,12 @@
         <v>1924</v>
       </c>
       <c r="B1085" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1086" t="s">
         <v>1926</v>
@@ -15415,12 +15421,12 @@
         <v>1943</v>
       </c>
       <c r="B1095" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B1096" t="s">
         <v>1945</v>
@@ -15495,12 +15501,12 @@
         <v>1962</v>
       </c>
       <c r="B1105" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B1106" t="s">
         <v>1964</v>
@@ -15511,20 +15517,20 @@
         <v>1965</v>
       </c>
       <c r="B1107" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="B1108" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B1109" t="s">
         <v>1968</v>
@@ -15559,12 +15565,12 @@
         <v>1975</v>
       </c>
       <c r="B1113" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B1114" t="s">
         <v>1977</v>
@@ -15575,12 +15581,12 @@
         <v>1978</v>
       </c>
       <c r="B1115" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B1116" t="s">
         <v>1980</v>
@@ -15735,12 +15741,12 @@
         <v>2017</v>
       </c>
       <c r="B1135" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B1136" t="s">
         <v>2019</v>
@@ -15751,12 +15757,12 @@
         <v>2020</v>
       </c>
       <c r="B1137" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B1138" t="s">
         <v>2022</v>
@@ -15767,12 +15773,12 @@
         <v>2023</v>
       </c>
       <c r="B1139" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B1140" t="s">
         <v>2025</v>
@@ -15791,28 +15797,28 @@
         <v>2028</v>
       </c>
       <c r="B1142" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B1143" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B1144" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B1145" t="s">
         <v>2032</v>
@@ -15895,12 +15901,12 @@
         <v>2051</v>
       </c>
       <c r="B1155" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="B1156" t="s">
         <v>2053</v>
@@ -15943,20 +15949,20 @@
         <v>2062</v>
       </c>
       <c r="B1161" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="B1162" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="B1163" t="s">
         <v>2065</v>
@@ -15991,12 +15997,12 @@
         <v>2072</v>
       </c>
       <c r="B1167" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B1168" t="s">
         <v>2074</v>
@@ -16023,28 +16029,28 @@
         <v>2079</v>
       </c>
       <c r="B1171" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="B1172" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="B1173" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="B1174" t="s">
         <v>2083</v>
@@ -16063,12 +16069,12 @@
         <v>2086</v>
       </c>
       <c r="B1176" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="B1177" t="s">
         <v>2088</v>
@@ -16087,12 +16093,12 @@
         <v>2091</v>
       </c>
       <c r="B1179" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="B1180" t="s">
         <v>2093</v>
@@ -16106,8 +16112,16 @@
         <v>2095</v>
       </c>
     </row>
+    <row r="1182" spans="1:2">
+      <c r="A1182" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>2097</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1181"/>
+  <autoFilter ref="A1:B1182"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2106">
   <si>
     <t>en</t>
   </si>
@@ -3148,6 +3148,12 @@
     <t>Hypixel</t>
   </si>
   <si>
+    <t>Hypixel (Abiphone)</t>
+  </si>
+  <si>
+    <t>"Hypixel" (Abiphone)</t>
+  </si>
+  <si>
     <t>Hypixel (Attribute Shard)</t>
   </si>
   <si>
@@ -3172,6 +3178,12 @@
     <t>"Hypixel" (įrankis)</t>
   </si>
   <si>
+    <t>Hypixel (Gemstone)</t>
+  </si>
+  <si>
+    <t>Hipikselis (brangakmenis)</t>
+  </si>
+  <si>
     <t>Hypixel (Minion)</t>
   </si>
   <si>
@@ -3190,6 +3202,12 @@
     <t>Hipikselis (NPC)</t>
   </si>
   <si>
+    <t>Hypixel (Pet Items)</t>
+  </si>
+  <si>
+    <t>Hypixel (Naminių gyvūnėlių reikmenys)</t>
+  </si>
+  <si>
     <t>Hypixel (Pets)</t>
   </si>
   <si>
@@ -3200,6 +3218,12 @@
   </si>
   <si>
     <t>"Hypixel" (Perdirbimo akmuo)</t>
+  </si>
+  <si>
+    <t>Hypixel (Runes)</t>
+  </si>
+  <si>
+    <t>Hipikselis (Runos)</t>
   </si>
   <si>
     <t>Hypixel (Sacks)</t>
@@ -6657,7 +6681,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1182"/>
+  <dimension ref="A1:B1186"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -11413,36 +11437,36 @@
         <v>1071</v>
       </c>
       <c r="B594" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B595" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B596" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B597" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B598" t="s">
         <v>1079</v>
@@ -11485,52 +11509,52 @@
         <v>1088</v>
       </c>
       <c r="B603" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B604" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B605" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="B606" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="B607" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="B608" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B609" t="s">
         <v>1098</v>
@@ -11637,60 +11661,60 @@
         <v>1123</v>
       </c>
       <c r="B622" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B623" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B624" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B625" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B626" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B627" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B628" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B629" t="s">
         <v>1136</v>
@@ -11701,156 +11725,156 @@
         <v>1137</v>
       </c>
       <c r="B630" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B631" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B632" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B633" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B634" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B635" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="B636" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B637" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="B638" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="B639" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="B640" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="B641" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="B642" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="B643" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="B644" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="B645" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B646" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="B647" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B648" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B649" t="s">
         <v>1164</v>
@@ -11861,68 +11885,68 @@
         <v>1165</v>
       </c>
       <c r="B650" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B651" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B652" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="B653" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="B654" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="B655" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B656" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B657" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B658" t="s">
         <v>1178</v>
@@ -12093,76 +12117,76 @@
         <v>1219</v>
       </c>
       <c r="B679" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B680" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B681" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B682" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B683" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B684" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B685" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="B686" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B687" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B688" t="s">
         <v>1235</v>
@@ -12269,124 +12293,124 @@
         <v>1260</v>
       </c>
       <c r="B701" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B702" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B703" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="B704" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B705" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="B706" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="B707" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="B708" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="B709" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="B710" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="B711" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="B712" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="B713" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="B714" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="B715" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B716" t="s">
         <v>1283</v>
@@ -12461,44 +12485,44 @@
         <v>1300</v>
       </c>
       <c r="B725" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B726" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="B727" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B728" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="B729" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B730" t="s">
         <v>1309</v>
@@ -12517,36 +12541,36 @@
         <v>1312</v>
       </c>
       <c r="B732" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B733" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B734" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B735" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B736" t="s">
         <v>1320</v>
@@ -12573,108 +12597,108 @@
         <v>1325</v>
       </c>
       <c r="B739" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B740" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B741" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B742" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B743" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B744" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="B745" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="B746" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="B747" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="B748" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="B749" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="B750" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="B751" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B752" t="s">
         <v>1347</v>
@@ -12757,52 +12781,52 @@
         <v>1366</v>
       </c>
       <c r="B762" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B763" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="B764" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="B765" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="B766" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="B767" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B768" t="s">
         <v>1376</v>
@@ -12821,36 +12845,36 @@
         <v>1379</v>
       </c>
       <c r="B770" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B771" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B772" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B773" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B774" t="s">
         <v>1387</v>
@@ -12933,164 +12957,164 @@
         <v>1406</v>
       </c>
       <c r="B784" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B785" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="B786" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="B787" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="B788" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="B789" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B790" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B791" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B792" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="B793" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B794" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B795" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B796" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="B797" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="B798" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="B799" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="B800" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="B801" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="B802" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B803" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B804" t="s">
         <v>1437</v>
@@ -13133,44 +13157,44 @@
         <v>1446</v>
       </c>
       <c r="B809" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B810" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="B811" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="B812" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="B813" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B814" t="s">
         <v>1455</v>
@@ -13181,132 +13205,132 @@
         <v>1456</v>
       </c>
       <c r="B815" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B816" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B817" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B818" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="B819" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B820" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B821" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="B822" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B823" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B824" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B825" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B826" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B827" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="B828" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="B829" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B830" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B831" t="s">
         <v>1484</v>
@@ -13325,60 +13349,60 @@
         <v>1487</v>
       </c>
       <c r="B833" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B834" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="B835" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="B836" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="B837" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="B838" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B839" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B840" t="s">
         <v>1498</v>
@@ -13421,52 +13445,52 @@
         <v>1507</v>
       </c>
       <c r="B845" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B846" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="B847" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
       <c r="B848" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="B849" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="B850" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B851" t="s">
         <v>1517</v>
@@ -13549,84 +13573,84 @@
         <v>1536</v>
       </c>
       <c r="B861" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B862" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="B863" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="B864" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="B865" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="B866" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B867" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B868" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B869" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B870" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B871" t="s">
         <v>1553</v>
@@ -13709,148 +13733,148 @@
         <v>1572</v>
       </c>
       <c r="B881" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B882" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="B883" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B884" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B885" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B886" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B887" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B888" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B889" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B890" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B891" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B892" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="B893" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="B894" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="B895" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="B896" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="B897" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B898" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B899" t="s">
         <v>1602</v>
@@ -13885,108 +13909,108 @@
         <v>1609</v>
       </c>
       <c r="B903" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B904" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B905" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B906" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B907" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B908" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B909" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="B910" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="B911" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="B912" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1624</v>
+        <v>1627</v>
       </c>
       <c r="B913" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="B914" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B915" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B916" t="s">
         <v>1631</v>
@@ -13997,52 +14021,52 @@
         <v>1632</v>
       </c>
       <c r="B917" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B918" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="B919" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="B920" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="B921" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="B922" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B923" t="s">
         <v>1642</v>
@@ -14061,44 +14085,44 @@
         <v>1645</v>
       </c>
       <c r="B925" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B926" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="B927" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="B928" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="B929" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B930" t="s">
         <v>1654</v>
@@ -14109,60 +14133,60 @@
         <v>1655</v>
       </c>
       <c r="B931" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B932" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B933" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="B934" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="B935" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="B936" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="B937" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B938" t="s">
         <v>1667</v>
@@ -14221,100 +14245,100 @@
         <v>1680</v>
       </c>
       <c r="B945" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B946" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="B947" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="B948" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B949" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="B950" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B951" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="B952" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="B953" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="B954" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="B955" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="B956" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B957" t="s">
         <v>1699</v>
@@ -14333,44 +14357,44 @@
         <v>1702</v>
       </c>
       <c r="B959" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B960" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="B961" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="B962" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="B963" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B964" t="s">
         <v>1711</v>
@@ -14405,44 +14429,44 @@
         <v>1718</v>
       </c>
       <c r="B968" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B969" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="B970" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="B971" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="B972" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B973" t="s">
         <v>1727</v>
@@ -14517,44 +14541,44 @@
         <v>1744</v>
       </c>
       <c r="B982" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B983" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="B984" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="B985" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="B986" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B987" t="s">
         <v>1753</v>
@@ -14565,68 +14589,68 @@
         <v>1754</v>
       </c>
       <c r="B988" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B989" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B990" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="B991" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="B992" t="s">
-        <v>1759</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="B993" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="B994" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B995" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B996" t="s">
         <v>1767</v>
@@ -14634,55 +14658,55 @@
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B997" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B998" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B999" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="B1000" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B1001" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1002" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B1003" t="s">
         <v>1780</v>
@@ -14717,92 +14741,92 @@
         <v>1787</v>
       </c>
       <c r="B1007" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B1008" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="B1009" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="B1010" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="B1011" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="B1012" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1013" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="B1014" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1798</v>
+        <v>1801</v>
       </c>
       <c r="B1015" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="B1016" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="B1017" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B1018" t="s">
         <v>1805</v>
@@ -14813,68 +14837,68 @@
         <v>1806</v>
       </c>
       <c r="B1019" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B1020" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="B1021" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="B1022" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="B1023" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="B1024" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1025" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B1026" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B1027" t="s">
         <v>1820</v>
@@ -14901,36 +14925,36 @@
         <v>1825</v>
       </c>
       <c r="B1030" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1031" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1032" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B1033" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1034" t="s">
         <v>1833</v>
@@ -14941,108 +14965,108 @@
         <v>1834</v>
       </c>
       <c r="B1035" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1036" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B1037" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="B1038" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="B1039" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B1040" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="B1041" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B1042" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="B1043" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B1044" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B1045" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B1046" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1047" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1048" t="s">
         <v>1857</v>
@@ -15165,36 +15189,36 @@
         <v>1886</v>
       </c>
       <c r="B1063" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B1064" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B1065" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1066" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B1067" t="s">
         <v>1894</v>
@@ -15245,140 +15269,140 @@
         <v>1905</v>
       </c>
       <c r="B1073" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1074" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B1075" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B1076" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="B1077" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1078" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="B1079" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="B1080" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="B1081" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="B1082" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1083" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="B1084" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B1085" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B1086" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="B1087" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B1088" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B1089" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1090" t="s">
         <v>1934</v>
@@ -15429,36 +15453,36 @@
         <v>1945</v>
       </c>
       <c r="B1096" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B1097" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="B1098" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="B1099" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="B1100" t="s">
         <v>1953</v>
@@ -15509,60 +15533,60 @@
         <v>1964</v>
       </c>
       <c r="B1106" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B1107" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B1108" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="B1109" t="s">
-        <v>1968</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="B1110" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="B1111" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="B1112" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1113" t="s">
         <v>1976</v>
@@ -15573,52 +15597,52 @@
         <v>1977</v>
       </c>
       <c r="B1114" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B1115" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B1116" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="B1117" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="B1118" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B1119" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B1120" t="s">
         <v>1988</v>
@@ -15749,108 +15773,108 @@
         <v>2019</v>
       </c>
       <c r="B1136" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B1137" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B1138" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B1139" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="B1140" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="B1141" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="B1142" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B1143" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="B1144" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="B1145" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="B1146" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="B1147" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="B1148" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B1149" t="s">
         <v>2040</v>
@@ -15909,36 +15933,36 @@
         <v>2053</v>
       </c>
       <c r="B1156" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="B1157" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="B1158" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="B1159" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="B1160" t="s">
         <v>2061</v>
@@ -15957,44 +15981,44 @@
         <v>2064</v>
       </c>
       <c r="B1162" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="B1163" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="B1164" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="B1165" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="B1166" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="B1167" t="s">
         <v>2073</v>
@@ -16005,123 +16029,155 @@
         <v>2074</v>
       </c>
       <c r="B1168" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="B1169" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="B1170" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="B1171" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="B1172" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="B1173" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="B1174" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="B1175" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="B1176" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="B1177" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="B1178" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="B1179" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="B1180" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="B1181" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="B1182" t="s">
-        <v>2097</v>
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:2">
+      <c r="A1183" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:2">
+      <c r="A1184" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2">
+      <c r="A1185" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:2">
+      <c r="A1186" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>2105</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1182"/>
+  <autoFilter ref="A1:B1186"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2108">
   <si>
     <t>en</t>
   </si>
@@ -4739,6 +4739,12 @@
   </si>
   <si>
     <t>Prof. Laytonas</t>
+  </si>
+  <si>
+    <t>Project Zomboid</t>
+  </si>
+  <si>
+    <t>Projektas "Zomboid</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -6681,7 +6687,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1186"/>
+  <dimension ref="A1:B1187"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13765,20 +13771,20 @@
         <v>1580</v>
       </c>
       <c r="B885" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B886" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B887" t="s">
         <v>1583</v>
@@ -13805,12 +13811,12 @@
         <v>1588</v>
       </c>
       <c r="B890" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B891" t="s">
         <v>1590</v>
@@ -13829,12 +13835,12 @@
         <v>1593</v>
       </c>
       <c r="B893" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B894" t="s">
         <v>1595</v>
@@ -13845,12 +13851,12 @@
         <v>1596</v>
       </c>
       <c r="B895" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B896" t="s">
         <v>1598</v>
@@ -13861,12 +13867,12 @@
         <v>1599</v>
       </c>
       <c r="B897" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B898" t="s">
         <v>1601</v>
@@ -13877,12 +13883,12 @@
         <v>1602</v>
       </c>
       <c r="B899" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B900" t="s">
         <v>1604</v>
@@ -13941,12 +13947,12 @@
         <v>1617</v>
       </c>
       <c r="B907" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B908" t="s">
         <v>1619</v>
@@ -13973,12 +13979,12 @@
         <v>1624</v>
       </c>
       <c r="B911" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B912" t="s">
         <v>1626</v>
@@ -13989,20 +13995,20 @@
         <v>1627</v>
       </c>
       <c r="B913" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B914" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B915" t="s">
         <v>1630</v>
@@ -14013,12 +14019,12 @@
         <v>1631</v>
       </c>
       <c r="B916" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B917" t="s">
         <v>1633</v>
@@ -14053,28 +14059,28 @@
         <v>1640</v>
       </c>
       <c r="B921" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B922" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B923" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B924" t="s">
         <v>1644</v>
@@ -14117,20 +14123,20 @@
         <v>1653</v>
       </c>
       <c r="B929" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B930" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B931" t="s">
         <v>1656</v>
@@ -14165,12 +14171,12 @@
         <v>1663</v>
       </c>
       <c r="B935" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B936" t="s">
         <v>1665</v>
@@ -14181,20 +14187,20 @@
         <v>1666</v>
       </c>
       <c r="B937" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B938" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B939" t="s">
         <v>1669</v>
@@ -14277,20 +14283,20 @@
         <v>1688</v>
       </c>
       <c r="B949" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B950" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B951" t="s">
         <v>1691</v>
@@ -14309,12 +14315,12 @@
         <v>1694</v>
       </c>
       <c r="B953" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B954" t="s">
         <v>1696</v>
@@ -14325,28 +14331,28 @@
         <v>1697</v>
       </c>
       <c r="B955" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B956" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B957" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B958" t="s">
         <v>1701</v>
@@ -14389,20 +14395,20 @@
         <v>1710</v>
       </c>
       <c r="B963" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B964" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B965" t="s">
         <v>1713</v>
@@ -14461,20 +14467,20 @@
         <v>1726</v>
       </c>
       <c r="B972" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B973" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B974" t="s">
         <v>1729</v>
@@ -14573,20 +14579,20 @@
         <v>1752</v>
       </c>
       <c r="B986" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B987" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B988" t="s">
         <v>1755</v>
@@ -14621,12 +14627,12 @@
         <v>1762</v>
       </c>
       <c r="B992" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B993" t="s">
         <v>1764</v>
@@ -14637,12 +14643,12 @@
         <v>1765</v>
       </c>
       <c r="B994" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B995" t="s">
         <v>1767</v>
@@ -14653,15 +14659,15 @@
         <v>1768</v>
       </c>
       <c r="B996" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B997" t="s">
         <v>1769</v>
-      </c>
-      <c r="B997" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="998" spans="1:2">
@@ -14685,12 +14691,12 @@
         <v>1775</v>
       </c>
       <c r="B1000" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B1001" t="s">
         <v>1777</v>
@@ -14709,12 +14715,12 @@
         <v>1780</v>
       </c>
       <c r="B1003" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B1004" t="s">
         <v>1782</v>
@@ -14773,20 +14779,20 @@
         <v>1795</v>
       </c>
       <c r="B1011" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1012" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B1013" t="s">
         <v>1798</v>
@@ -14805,12 +14811,12 @@
         <v>1801</v>
       </c>
       <c r="B1015" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B1016" t="s">
         <v>1803</v>
@@ -14821,20 +14827,20 @@
         <v>1804</v>
       </c>
       <c r="B1017" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B1018" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B1019" t="s">
         <v>1807</v>
@@ -14869,20 +14875,20 @@
         <v>1814</v>
       </c>
       <c r="B1023" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1024" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B1025" t="s">
         <v>1817</v>
@@ -14901,12 +14907,12 @@
         <v>1820</v>
       </c>
       <c r="B1027" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B1028" t="s">
         <v>1822</v>
@@ -14957,12 +14963,12 @@
         <v>1833</v>
       </c>
       <c r="B1034" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1035" t="s">
         <v>1835</v>
@@ -14997,12 +15003,12 @@
         <v>1842</v>
       </c>
       <c r="B1039" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B1040" t="s">
         <v>1844</v>
@@ -15013,12 +15019,12 @@
         <v>1845</v>
       </c>
       <c r="B1041" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B1042" t="s">
         <v>1847</v>
@@ -15037,12 +15043,12 @@
         <v>1850</v>
       </c>
       <c r="B1044" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B1045" t="s">
         <v>1852</v>
@@ -15069,12 +15075,12 @@
         <v>1857</v>
       </c>
       <c r="B1048" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1049" t="s">
         <v>1859</v>
@@ -15221,12 +15227,12 @@
         <v>1894</v>
       </c>
       <c r="B1067" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B1068" t="s">
         <v>1896</v>
@@ -15301,12 +15307,12 @@
         <v>1913</v>
       </c>
       <c r="B1077" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1078" t="s">
         <v>1915</v>
@@ -15325,12 +15331,12 @@
         <v>1918</v>
       </c>
       <c r="B1080" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="B1081" t="s">
         <v>1920</v>
@@ -15341,12 +15347,12 @@
         <v>1921</v>
       </c>
       <c r="B1082" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1083" t="s">
         <v>1923</v>
@@ -15357,12 +15363,12 @@
         <v>1924</v>
       </c>
       <c r="B1084" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1085" t="s">
         <v>1926</v>
@@ -15381,12 +15387,12 @@
         <v>1929</v>
       </c>
       <c r="B1087" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1088" t="s">
         <v>1931</v>
@@ -15405,12 +15411,12 @@
         <v>1934</v>
       </c>
       <c r="B1090" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B1091" t="s">
         <v>1936</v>
@@ -15485,12 +15491,12 @@
         <v>1953</v>
       </c>
       <c r="B1100" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="B1101" t="s">
         <v>1955</v>
@@ -15565,12 +15571,12 @@
         <v>1972</v>
       </c>
       <c r="B1110" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B1111" t="s">
         <v>1974</v>
@@ -15581,20 +15587,20 @@
         <v>1975</v>
       </c>
       <c r="B1112" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B1113" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B1114" t="s">
         <v>1978</v>
@@ -15629,12 +15635,12 @@
         <v>1985</v>
       </c>
       <c r="B1118" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B1119" t="s">
         <v>1987</v>
@@ -15645,12 +15651,12 @@
         <v>1988</v>
       </c>
       <c r="B1120" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B1121" t="s">
         <v>1990</v>
@@ -15805,12 +15811,12 @@
         <v>2027</v>
       </c>
       <c r="B1140" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B1141" t="s">
         <v>2029</v>
@@ -15821,12 +15827,12 @@
         <v>2030</v>
       </c>
       <c r="B1142" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B1143" t="s">
         <v>2032</v>
@@ -15837,12 +15843,12 @@
         <v>2033</v>
       </c>
       <c r="B1144" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B1145" t="s">
         <v>2035</v>
@@ -15861,28 +15867,28 @@
         <v>2038</v>
       </c>
       <c r="B1147" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B1148" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="B1149" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B1150" t="s">
         <v>2042</v>
@@ -15965,12 +15971,12 @@
         <v>2061</v>
       </c>
       <c r="B1160" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="B1161" t="s">
         <v>2063</v>
@@ -16013,20 +16019,20 @@
         <v>2072</v>
       </c>
       <c r="B1166" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B1167" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="B1168" t="s">
         <v>2075</v>
@@ -16061,12 +16067,12 @@
         <v>2082</v>
       </c>
       <c r="B1172" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="B1173" t="s">
         <v>2084</v>
@@ -16093,28 +16099,28 @@
         <v>2089</v>
       </c>
       <c r="B1176" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="B1177" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="B1178" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="B1179" t="s">
         <v>2093</v>
@@ -16133,12 +16139,12 @@
         <v>2096</v>
       </c>
       <c r="B1181" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B1182" t="s">
         <v>2098</v>
@@ -16157,12 +16163,12 @@
         <v>2101</v>
       </c>
       <c r="B1184" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B1185" t="s">
         <v>2103</v>
@@ -16176,8 +16182,16 @@
         <v>2105</v>
       </c>
     </row>
+    <row r="1187" spans="1:2">
+      <c r="A1187" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>2107</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1186"/>
+  <autoFilter ref="A1:B1187"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2111">
   <si>
     <t>en</t>
   </si>
@@ -5078,6 +5078,12 @@
   </si>
   <si>
     <t>Mordoro šešėliai</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>Ryklys</t>
   </si>
   <si>
     <t>Sheep</t>
@@ -6690,7 +6696,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1188"/>
+  <dimension ref="A1:B1189"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14302,20 +14308,20 @@
         <v>1691</v>
       </c>
       <c r="B951" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B952" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B953" t="s">
         <v>1694</v>
@@ -14334,12 +14340,12 @@
         <v>1697</v>
       </c>
       <c r="B955" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B956" t="s">
         <v>1699</v>
@@ -14350,28 +14356,28 @@
         <v>1700</v>
       </c>
       <c r="B957" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B958" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B959" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B960" t="s">
         <v>1704</v>
@@ -14414,20 +14420,20 @@
         <v>1713</v>
       </c>
       <c r="B965" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B966" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B967" t="s">
         <v>1716</v>
@@ -14486,20 +14492,20 @@
         <v>1729</v>
       </c>
       <c r="B974" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B975" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B976" t="s">
         <v>1732</v>
@@ -14598,20 +14604,20 @@
         <v>1755</v>
       </c>
       <c r="B988" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B989" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B990" t="s">
         <v>1758</v>
@@ -14646,12 +14652,12 @@
         <v>1765</v>
       </c>
       <c r="B994" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B995" t="s">
         <v>1767</v>
@@ -14662,12 +14668,12 @@
         <v>1768</v>
       </c>
       <c r="B996" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B997" t="s">
         <v>1770</v>
@@ -14678,15 +14684,15 @@
         <v>1771</v>
       </c>
       <c r="B998" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B999" t="s">
         <v>1772</v>
-      </c>
-      <c r="B999" t="s">
-        <v>1773</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
@@ -14710,12 +14716,12 @@
         <v>1778</v>
       </c>
       <c r="B1002" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B1003" t="s">
         <v>1780</v>
@@ -14734,12 +14740,12 @@
         <v>1783</v>
       </c>
       <c r="B1005" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B1006" t="s">
         <v>1785</v>
@@ -14798,20 +14804,20 @@
         <v>1798</v>
       </c>
       <c r="B1013" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B1014" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B1015" t="s">
         <v>1801</v>
@@ -14830,12 +14836,12 @@
         <v>1804</v>
       </c>
       <c r="B1017" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B1018" t="s">
         <v>1806</v>
@@ -14846,20 +14852,20 @@
         <v>1807</v>
       </c>
       <c r="B1019" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1020" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1021" t="s">
         <v>1810</v>
@@ -14894,20 +14900,20 @@
         <v>1817</v>
       </c>
       <c r="B1025" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1026" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B1027" t="s">
         <v>1820</v>
@@ -14926,12 +14932,12 @@
         <v>1823</v>
       </c>
       <c r="B1029" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1030" t="s">
         <v>1825</v>
@@ -14982,12 +14988,12 @@
         <v>1836</v>
       </c>
       <c r="B1036" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B1037" t="s">
         <v>1838</v>
@@ -15022,12 +15028,12 @@
         <v>1845</v>
       </c>
       <c r="B1041" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B1042" t="s">
         <v>1847</v>
@@ -15038,12 +15044,12 @@
         <v>1848</v>
       </c>
       <c r="B1043" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B1044" t="s">
         <v>1850</v>
@@ -15062,12 +15068,12 @@
         <v>1853</v>
       </c>
       <c r="B1046" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1047" t="s">
         <v>1855</v>
@@ -15094,12 +15100,12 @@
         <v>1860</v>
       </c>
       <c r="B1050" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1051" t="s">
         <v>1862</v>
@@ -15246,12 +15252,12 @@
         <v>1897</v>
       </c>
       <c r="B1069" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B1070" t="s">
         <v>1899</v>
@@ -15326,12 +15332,12 @@
         <v>1916</v>
       </c>
       <c r="B1079" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="B1080" t="s">
         <v>1918</v>
@@ -15350,12 +15356,12 @@
         <v>1921</v>
       </c>
       <c r="B1082" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1083" t="s">
         <v>1923</v>
@@ -15366,12 +15372,12 @@
         <v>1924</v>
       </c>
       <c r="B1084" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1085" t="s">
         <v>1926</v>
@@ -15382,12 +15388,12 @@
         <v>1927</v>
       </c>
       <c r="B1086" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="B1087" t="s">
         <v>1929</v>
@@ -15406,12 +15412,12 @@
         <v>1932</v>
       </c>
       <c r="B1089" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1090" t="s">
         <v>1934</v>
@@ -15430,12 +15436,12 @@
         <v>1937</v>
       </c>
       <c r="B1092" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="B1093" t="s">
         <v>1939</v>
@@ -15510,12 +15516,12 @@
         <v>1956</v>
       </c>
       <c r="B1102" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B1103" t="s">
         <v>1958</v>
@@ -15590,12 +15596,12 @@
         <v>1975</v>
       </c>
       <c r="B1112" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B1113" t="s">
         <v>1977</v>
@@ -15606,20 +15612,20 @@
         <v>1978</v>
       </c>
       <c r="B1114" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B1115" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B1116" t="s">
         <v>1981</v>
@@ -15654,12 +15660,12 @@
         <v>1988</v>
       </c>
       <c r="B1120" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B1121" t="s">
         <v>1990</v>
@@ -15670,12 +15676,12 @@
         <v>1991</v>
       </c>
       <c r="B1122" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1123" t="s">
         <v>1993</v>
@@ -15830,12 +15836,12 @@
         <v>2030</v>
       </c>
       <c r="B1142" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B1143" t="s">
         <v>2032</v>
@@ -15846,12 +15852,12 @@
         <v>2033</v>
       </c>
       <c r="B1144" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B1145" t="s">
         <v>2035</v>
@@ -15862,12 +15868,12 @@
         <v>2036</v>
       </c>
       <c r="B1146" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B1147" t="s">
         <v>2038</v>
@@ -15886,28 +15892,28 @@
         <v>2041</v>
       </c>
       <c r="B1149" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B1150" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="B1151" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B1152" t="s">
         <v>2045</v>
@@ -15990,12 +15996,12 @@
         <v>2064</v>
       </c>
       <c r="B1162" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="B1163" t="s">
         <v>2066</v>
@@ -16038,20 +16044,20 @@
         <v>2075</v>
       </c>
       <c r="B1168" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="B1169" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="B1170" t="s">
         <v>2078</v>
@@ -16086,12 +16092,12 @@
         <v>2085</v>
       </c>
       <c r="B1174" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="B1175" t="s">
         <v>2087</v>
@@ -16118,28 +16124,28 @@
         <v>2092</v>
       </c>
       <c r="B1178" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="B1179" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="B1180" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="B1181" t="s">
         <v>2096</v>
@@ -16158,12 +16164,12 @@
         <v>2099</v>
       </c>
       <c r="B1183" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B1184" t="s">
         <v>2101</v>
@@ -16182,12 +16188,12 @@
         <v>2104</v>
       </c>
       <c r="B1186" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="B1187" t="s">
         <v>2106</v>
@@ -16201,8 +16207,16 @@
         <v>2108</v>
       </c>
     </row>
+    <row r="1189" spans="1:2">
+      <c r="A1189" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>2110</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1188"/>
+  <autoFilter ref="A1:B1189"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -1729,6 +1729,12 @@
     <t>Pasakos</t>
   </si>
   <si>
+    <t>Fall Drop</t>
+  </si>
+  <si>
+    <t>Rudens kritimas</t>
+  </si>
+  <si>
     <t>Fall Guys</t>
   </si>
   <si>
@@ -6344,12 +6350,6 @@
   </si>
   <si>
     <t>Hipikselis (Mutacijos) Žyma</t>
-  </si>
-  <si>
-    <t>Fall Drop</t>
-  </si>
-  <si>
-    <t>Rudens kritimas</t>
   </si>
 </sst>
 </file>
@@ -9308,12 +9308,12 @@
         <v>572</v>
       </c>
       <c r="B326" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B327" t="s">
         <v>574</v>
@@ -9356,12 +9356,12 @@
         <v>583</v>
       </c>
       <c r="B332" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B333" t="s">
         <v>585</v>
@@ -9428,12 +9428,12 @@
         <v>600</v>
       </c>
       <c r="B341" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B342" t="s">
         <v>602</v>
@@ -10164,28 +10164,28 @@
         <v>783</v>
       </c>
       <c r="B433" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B434" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B435" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B436" t="s">
         <v>787</v>
@@ -10284,12 +10284,12 @@
         <v>810</v>
       </c>
       <c r="B448" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B449" t="s">
         <v>812</v>
@@ -10300,12 +10300,12 @@
         <v>813</v>
       </c>
       <c r="B450" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B451" t="s">
         <v>815</v>
@@ -10420,12 +10420,12 @@
         <v>842</v>
       </c>
       <c r="B465" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B466" t="s">
         <v>844</v>
@@ -10436,20 +10436,20 @@
         <v>845</v>
       </c>
       <c r="B467" t="s">
-        <v>561</v>
+        <v>846</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B468" t="s">
-        <v>846</v>
+        <v>561</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B469" t="s">
         <v>848</v>
@@ -10460,12 +10460,12 @@
         <v>849</v>
       </c>
       <c r="B470" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B471" t="s">
         <v>851</v>
@@ -10484,23 +10484,23 @@
         <v>854</v>
       </c>
       <c r="B473" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B474" t="s">
-        <v>561</v>
+        <v>856</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B475" t="s">
-        <v>857</v>
+        <v>561</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -10508,12 +10508,12 @@
         <v>858</v>
       </c>
       <c r="B476" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B477" t="s">
         <v>860</v>
@@ -10564,20 +10564,20 @@
         <v>871</v>
       </c>
       <c r="B483" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B484" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B485" t="s">
         <v>874</v>
@@ -10588,12 +10588,12 @@
         <v>875</v>
       </c>
       <c r="B486" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B487" t="s">
         <v>877</v>
@@ -10604,28 +10604,28 @@
         <v>878</v>
       </c>
       <c r="B488" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B489" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B490" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B491" t="s">
         <v>882</v>
@@ -10812,12 +10812,12 @@
         <v>927</v>
       </c>
       <c r="B514" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B515" t="s">
         <v>929</v>
@@ -10964,12 +10964,12 @@
         <v>964</v>
       </c>
       <c r="B533" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B534" t="s">
         <v>966</v>
@@ -10988,20 +10988,20 @@
         <v>969</v>
       </c>
       <c r="B536" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B537" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B538" t="s">
         <v>972</v>
@@ -11020,28 +11020,28 @@
         <v>975</v>
       </c>
       <c r="B540" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B541" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B542" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B543" t="s">
         <v>979</v>
@@ -11076,20 +11076,20 @@
         <v>986</v>
       </c>
       <c r="B547" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B548" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B549" t="s">
         <v>989</v>
@@ -11100,12 +11100,12 @@
         <v>990</v>
       </c>
       <c r="B550" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B551" t="s">
         <v>992</v>
@@ -11116,12 +11116,12 @@
         <v>993</v>
       </c>
       <c r="B552" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B553" t="s">
         <v>995</v>
@@ -11220,12 +11220,12 @@
         <v>1018</v>
       </c>
       <c r="B565" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B566" t="s">
         <v>1020</v>
@@ -11252,12 +11252,12 @@
         <v>1025</v>
       </c>
       <c r="B569" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B570" t="s">
         <v>1027</v>
@@ -11308,12 +11308,12 @@
         <v>1038</v>
       </c>
       <c r="B576" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B577" t="s">
         <v>1040</v>
@@ -11324,28 +11324,28 @@
         <v>1041</v>
       </c>
       <c r="B578" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B579" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B580" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B581" t="s">
         <v>1045</v>
@@ -11492,12 +11492,12 @@
         <v>1080</v>
       </c>
       <c r="B599" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B600" t="s">
         <v>1082</v>
@@ -11564,28 +11564,28 @@
         <v>1097</v>
       </c>
       <c r="B608" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B609" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B610" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B611" t="s">
         <v>1101</v>
@@ -11716,12 +11716,12 @@
         <v>1132</v>
       </c>
       <c r="B627" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B628" t="s">
         <v>1134</v>
@@ -11740,12 +11740,12 @@
         <v>1137</v>
       </c>
       <c r="B630" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B631" t="s">
         <v>1139</v>
@@ -11780,12 +11780,12 @@
         <v>1146</v>
       </c>
       <c r="B635" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B636" t="s">
         <v>1148</v>
@@ -11796,12 +11796,12 @@
         <v>1149</v>
       </c>
       <c r="B637" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B638" t="s">
         <v>1151</v>
@@ -11820,52 +11820,52 @@
         <v>1154</v>
       </c>
       <c r="B640" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B641" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B642" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B643" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B644" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B645" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B646" t="s">
         <v>1161</v>
@@ -11876,36 +11876,36 @@
         <v>1162</v>
       </c>
       <c r="B647" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B648" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B649" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B650" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B651" t="s">
         <v>1167</v>
@@ -11940,28 +11940,28 @@
         <v>1174</v>
       </c>
       <c r="B655" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B656" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B657" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B658" t="s">
         <v>1178</v>
@@ -11972,12 +11972,12 @@
         <v>1179</v>
       </c>
       <c r="B659" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B660" t="s">
         <v>1181</v>
@@ -12172,12 +12172,12 @@
         <v>1228</v>
       </c>
       <c r="B684" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B685" t="s">
         <v>1230</v>
@@ -12204,20 +12204,20 @@
         <v>1235</v>
       </c>
       <c r="B688" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B689" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B690" t="s">
         <v>1238</v>
@@ -12348,12 +12348,12 @@
         <v>1269</v>
       </c>
       <c r="B706" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B707" t="s">
         <v>1271</v>
@@ -12364,20 +12364,20 @@
         <v>1272</v>
       </c>
       <c r="B708" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B709" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B710" t="s">
         <v>1275</v>
@@ -12388,28 +12388,28 @@
         <v>1276</v>
       </c>
       <c r="B711" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B712" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B713" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B714" t="s">
         <v>1280</v>
@@ -12428,20 +12428,20 @@
         <v>1283</v>
       </c>
       <c r="B716" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B717" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B718" t="s">
         <v>1286</v>
@@ -12540,20 +12540,20 @@
         <v>1309</v>
       </c>
       <c r="B730" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B731" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B732" t="s">
         <v>1312</v>
@@ -12596,12 +12596,12 @@
         <v>1321</v>
       </c>
       <c r="B737" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B738" t="s">
         <v>1323</v>
@@ -12652,12 +12652,12 @@
         <v>1334</v>
       </c>
       <c r="B744" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B745" t="s">
         <v>1336</v>
@@ -12684,20 +12684,20 @@
         <v>1341</v>
       </c>
       <c r="B748" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B749" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B750" t="s">
         <v>1344</v>
@@ -12716,20 +12716,20 @@
         <v>1347</v>
       </c>
       <c r="B752" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B753" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B754" t="s">
         <v>1350</v>
@@ -12836,28 +12836,28 @@
         <v>1375</v>
       </c>
       <c r="B767" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B768" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B769" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B770" t="s">
         <v>1379</v>
@@ -12900,12 +12900,12 @@
         <v>1388</v>
       </c>
       <c r="B775" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B776" t="s">
         <v>1390</v>
@@ -13012,28 +13012,28 @@
         <v>1415</v>
       </c>
       <c r="B789" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B790" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B791" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B792" t="s">
         <v>1419</v>
@@ -13052,12 +13052,12 @@
         <v>1422</v>
       </c>
       <c r="B794" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B795" t="s">
         <v>1424</v>
@@ -13076,12 +13076,12 @@
         <v>1427</v>
       </c>
       <c r="B797" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B798" t="s">
         <v>1429</v>
@@ -13100,28 +13100,28 @@
         <v>1432</v>
       </c>
       <c r="B800" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B801" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B802" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B803" t="s">
         <v>1436</v>
@@ -13132,20 +13132,20 @@
         <v>1437</v>
       </c>
       <c r="B804" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B805" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B806" t="s">
         <v>1440</v>
@@ -13212,20 +13212,20 @@
         <v>1455</v>
       </c>
       <c r="B814" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B815" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B816" t="s">
         <v>1458</v>
@@ -13260,12 +13260,12 @@
         <v>1465</v>
       </c>
       <c r="B820" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B821" t="s">
         <v>1467</v>
@@ -13284,12 +13284,12 @@
         <v>1470</v>
       </c>
       <c r="B823" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B824" t="s">
         <v>1472</v>
@@ -13308,12 +13308,12 @@
         <v>1475</v>
       </c>
       <c r="B826" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B827" t="s">
         <v>1477</v>
@@ -13340,12 +13340,12 @@
         <v>1482</v>
       </c>
       <c r="B830" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B831" t="s">
         <v>1484</v>
@@ -13356,12 +13356,12 @@
         <v>1485</v>
       </c>
       <c r="B832" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B833" t="s">
         <v>1487</v>
@@ -13404,36 +13404,36 @@
         <v>1496</v>
       </c>
       <c r="B838" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B839" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B840" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B841" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B842" t="s">
         <v>1501</v>
@@ -13500,28 +13500,28 @@
         <v>1516</v>
       </c>
       <c r="B850" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B851" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B852" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B853" t="s">
         <v>1520</v>
@@ -13628,20 +13628,20 @@
         <v>1545</v>
       </c>
       <c r="B866" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B867" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B868" t="s">
         <v>1548</v>
@@ -13660,12 +13660,12 @@
         <v>1551</v>
       </c>
       <c r="B870" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B871" t="s">
         <v>1553</v>
@@ -13676,12 +13676,12 @@
         <v>1554</v>
       </c>
       <c r="B872" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B873" t="s">
         <v>1556</v>
@@ -13796,20 +13796,20 @@
         <v>1583</v>
       </c>
       <c r="B887" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B888" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B889" t="s">
         <v>1586</v>
@@ -13836,12 +13836,12 @@
         <v>1591</v>
       </c>
       <c r="B892" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B893" t="s">
         <v>1593</v>
@@ -13860,12 +13860,12 @@
         <v>1596</v>
       </c>
       <c r="B895" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B896" t="s">
         <v>1598</v>
@@ -13876,12 +13876,12 @@
         <v>1599</v>
       </c>
       <c r="B897" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B898" t="s">
         <v>1601</v>
@@ -13892,12 +13892,12 @@
         <v>1602</v>
       </c>
       <c r="B899" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B900" t="s">
         <v>1604</v>
@@ -13908,12 +13908,12 @@
         <v>1605</v>
       </c>
       <c r="B901" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B902" t="s">
         <v>1607</v>
@@ -13972,12 +13972,12 @@
         <v>1620</v>
       </c>
       <c r="B909" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B910" t="s">
         <v>1622</v>
@@ -14004,12 +14004,12 @@
         <v>1627</v>
       </c>
       <c r="B913" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B914" t="s">
         <v>1629</v>
@@ -14020,20 +14020,20 @@
         <v>1630</v>
       </c>
       <c r="B915" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B916" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B917" t="s">
         <v>1633</v>
@@ -14044,12 +14044,12 @@
         <v>1634</v>
       </c>
       <c r="B918" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B919" t="s">
         <v>1636</v>
@@ -14084,28 +14084,28 @@
         <v>1643</v>
       </c>
       <c r="B923" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B924" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B925" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B926" t="s">
         <v>1647</v>
@@ -14148,20 +14148,20 @@
         <v>1656</v>
       </c>
       <c r="B931" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B932" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B933" t="s">
         <v>1659</v>
@@ -14196,12 +14196,12 @@
         <v>1666</v>
       </c>
       <c r="B937" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B938" t="s">
         <v>1668</v>
@@ -14212,20 +14212,20 @@
         <v>1669</v>
       </c>
       <c r="B939" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B940" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B941" t="s">
         <v>1672</v>
@@ -14316,20 +14316,20 @@
         <v>1693</v>
       </c>
       <c r="B952" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B953" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B954" t="s">
         <v>1696</v>
@@ -14348,12 +14348,12 @@
         <v>1699</v>
       </c>
       <c r="B956" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B957" t="s">
         <v>1701</v>
@@ -14364,28 +14364,28 @@
         <v>1702</v>
       </c>
       <c r="B958" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B959" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B960" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B961" t="s">
         <v>1706</v>
@@ -14428,20 +14428,20 @@
         <v>1715</v>
       </c>
       <c r="B966" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B967" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B968" t="s">
         <v>1718</v>
@@ -14500,20 +14500,20 @@
         <v>1731</v>
       </c>
       <c r="B975" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B976" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B977" t="s">
         <v>1734</v>
@@ -14612,20 +14612,20 @@
         <v>1757</v>
       </c>
       <c r="B989" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B990" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B991" t="s">
         <v>1760</v>
@@ -14660,12 +14660,12 @@
         <v>1767</v>
       </c>
       <c r="B995" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B996" t="s">
         <v>1769</v>
@@ -14676,12 +14676,12 @@
         <v>1770</v>
       </c>
       <c r="B997" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B998" t="s">
         <v>1772</v>
@@ -14692,15 +14692,15 @@
         <v>1773</v>
       </c>
       <c r="B999" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B1000" t="s">
         <v>1774</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
@@ -14724,12 +14724,12 @@
         <v>1780</v>
       </c>
       <c r="B1003" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B1004" t="s">
         <v>1782</v>
@@ -14748,12 +14748,12 @@
         <v>1785</v>
       </c>
       <c r="B1006" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B1007" t="s">
         <v>1787</v>
@@ -14812,20 +14812,20 @@
         <v>1800</v>
       </c>
       <c r="B1014" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B1015" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B1016" t="s">
         <v>1803</v>
@@ -14844,12 +14844,12 @@
         <v>1806</v>
       </c>
       <c r="B1018" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B1019" t="s">
         <v>1808</v>
@@ -14860,20 +14860,20 @@
         <v>1809</v>
       </c>
       <c r="B1020" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B1021" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1022" t="s">
         <v>1812</v>
@@ -14908,20 +14908,20 @@
         <v>1819</v>
       </c>
       <c r="B1026" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B1027" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B1028" t="s">
         <v>1822</v>
@@ -14940,12 +14940,12 @@
         <v>1825</v>
       </c>
       <c r="B1030" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1031" t="s">
         <v>1827</v>
@@ -14996,12 +14996,12 @@
         <v>1838</v>
       </c>
       <c r="B1037" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1038" t="s">
         <v>1840</v>
@@ -15036,12 +15036,12 @@
         <v>1847</v>
       </c>
       <c r="B1042" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B1043" t="s">
         <v>1849</v>
@@ -15052,12 +15052,12 @@
         <v>1850</v>
       </c>
       <c r="B1044" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B1045" t="s">
         <v>1852</v>
@@ -15076,12 +15076,12 @@
         <v>1855</v>
       </c>
       <c r="B1047" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1048" t="s">
         <v>1857</v>
@@ -15108,12 +15108,12 @@
         <v>1862</v>
       </c>
       <c r="B1051" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1052" t="s">
         <v>1864</v>
@@ -15260,12 +15260,12 @@
         <v>1899</v>
       </c>
       <c r="B1070" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B1071" t="s">
         <v>1901</v>
@@ -15340,12 +15340,12 @@
         <v>1918</v>
       </c>
       <c r="B1080" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="B1081" t="s">
         <v>1920</v>
@@ -15364,12 +15364,12 @@
         <v>1923</v>
       </c>
       <c r="B1083" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B1084" t="s">
         <v>1925</v>
@@ -15380,12 +15380,12 @@
         <v>1926</v>
       </c>
       <c r="B1085" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1086" t="s">
         <v>1928</v>
@@ -15396,12 +15396,12 @@
         <v>1929</v>
       </c>
       <c r="B1087" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1088" t="s">
         <v>1931</v>
@@ -15420,12 +15420,12 @@
         <v>1934</v>
       </c>
       <c r="B1090" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B1091" t="s">
         <v>1936</v>
@@ -15444,12 +15444,12 @@
         <v>1939</v>
       </c>
       <c r="B1093" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B1094" t="s">
         <v>1941</v>
@@ -15524,12 +15524,12 @@
         <v>1958</v>
       </c>
       <c r="B1103" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="B1104" t="s">
         <v>1960</v>
@@ -15604,12 +15604,12 @@
         <v>1977</v>
       </c>
       <c r="B1113" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B1114" t="s">
         <v>1979</v>
@@ -15620,20 +15620,20 @@
         <v>1980</v>
       </c>
       <c r="B1115" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="B1116" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B1117" t="s">
         <v>1983</v>
@@ -15668,12 +15668,12 @@
         <v>1990</v>
       </c>
       <c r="B1121" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="B1122" t="s">
         <v>1992</v>
@@ -15684,12 +15684,12 @@
         <v>1993</v>
       </c>
       <c r="B1123" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B1124" t="s">
         <v>1995</v>
@@ -15844,12 +15844,12 @@
         <v>2032</v>
       </c>
       <c r="B1143" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B1144" t="s">
         <v>2034</v>
@@ -15860,12 +15860,12 @@
         <v>2035</v>
       </c>
       <c r="B1145" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="B1146" t="s">
         <v>2037</v>
@@ -15876,12 +15876,12 @@
         <v>2038</v>
       </c>
       <c r="B1147" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B1148" t="s">
         <v>2040</v>
@@ -15900,28 +15900,28 @@
         <v>2043</v>
       </c>
       <c r="B1150" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B1151" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="B1152" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B1153" t="s">
         <v>2047</v>
@@ -16004,12 +16004,12 @@
         <v>2066</v>
       </c>
       <c r="B1163" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="B1164" t="s">
         <v>2068</v>
@@ -16052,20 +16052,20 @@
         <v>2077</v>
       </c>
       <c r="B1169" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="B1170" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="B1171" t="s">
         <v>2080</v>
@@ -16100,12 +16100,12 @@
         <v>2087</v>
       </c>
       <c r="B1175" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="B1176" t="s">
         <v>2089</v>
@@ -16132,28 +16132,28 @@
         <v>2094</v>
       </c>
       <c r="B1179" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="B1180" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="B1181" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B1182" t="s">
         <v>2098</v>
@@ -16172,12 +16172,12 @@
         <v>2101</v>
       </c>
       <c r="B1184" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B1185" t="s">
         <v>2103</v>
@@ -16196,12 +16196,12 @@
         <v>2106</v>
       </c>
       <c r="B1187" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="B1188" t="s">
         <v>2108</v>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2113">
   <si>
     <t>en</t>
   </si>
@@ -4718,6 +4718,12 @@
   </si>
   <si>
     <t>Plėšrūnas</t>
+  </si>
+  <si>
+    <t>Prehistoric Creature</t>
+  </si>
+  <si>
+    <t>Priešistorinis padaras</t>
   </si>
   <si>
     <t>Present</t>
@@ -6696,7 +6702,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1189"/>
+  <dimension ref="A1:B1190"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13804,20 +13810,20 @@
         <v>1585</v>
       </c>
       <c r="B888" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B889" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B890" t="s">
         <v>1588</v>
@@ -13844,12 +13850,12 @@
         <v>1593</v>
       </c>
       <c r="B893" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B894" t="s">
         <v>1595</v>
@@ -13868,12 +13874,12 @@
         <v>1598</v>
       </c>
       <c r="B896" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B897" t="s">
         <v>1600</v>
@@ -13884,12 +13890,12 @@
         <v>1601</v>
       </c>
       <c r="B898" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B899" t="s">
         <v>1603</v>
@@ -13900,12 +13906,12 @@
         <v>1604</v>
       </c>
       <c r="B900" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B901" t="s">
         <v>1606</v>
@@ -13916,12 +13922,12 @@
         <v>1607</v>
       </c>
       <c r="B902" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B903" t="s">
         <v>1609</v>
@@ -13980,12 +13986,12 @@
         <v>1622</v>
       </c>
       <c r="B910" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B911" t="s">
         <v>1624</v>
@@ -14012,12 +14018,12 @@
         <v>1629</v>
       </c>
       <c r="B914" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B915" t="s">
         <v>1631</v>
@@ -14028,20 +14034,20 @@
         <v>1632</v>
       </c>
       <c r="B916" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B917" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B918" t="s">
         <v>1635</v>
@@ -14052,12 +14058,12 @@
         <v>1636</v>
       </c>
       <c r="B919" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B920" t="s">
         <v>1638</v>
@@ -14092,28 +14098,28 @@
         <v>1645</v>
       </c>
       <c r="B924" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B925" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B926" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B927" t="s">
         <v>1649</v>
@@ -14156,20 +14162,20 @@
         <v>1658</v>
       </c>
       <c r="B932" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B933" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B934" t="s">
         <v>1661</v>
@@ -14204,12 +14210,12 @@
         <v>1668</v>
       </c>
       <c r="B938" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B939" t="s">
         <v>1670</v>
@@ -14220,20 +14226,20 @@
         <v>1671</v>
       </c>
       <c r="B940" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B941" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B942" t="s">
         <v>1674</v>
@@ -14324,20 +14330,20 @@
         <v>1695</v>
       </c>
       <c r="B953" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B954" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B955" t="s">
         <v>1698</v>
@@ -14356,12 +14362,12 @@
         <v>1701</v>
       </c>
       <c r="B957" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B958" t="s">
         <v>1703</v>
@@ -14372,28 +14378,28 @@
         <v>1704</v>
       </c>
       <c r="B959" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B960" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B961" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B962" t="s">
         <v>1708</v>
@@ -14436,20 +14442,20 @@
         <v>1717</v>
       </c>
       <c r="B967" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B968" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B969" t="s">
         <v>1720</v>
@@ -14508,20 +14514,20 @@
         <v>1733</v>
       </c>
       <c r="B976" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B977" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B978" t="s">
         <v>1736</v>
@@ -14620,20 +14626,20 @@
         <v>1759</v>
       </c>
       <c r="B990" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B991" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B992" t="s">
         <v>1762</v>
@@ -14668,12 +14674,12 @@
         <v>1769</v>
       </c>
       <c r="B996" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B997" t="s">
         <v>1771</v>
@@ -14684,12 +14690,12 @@
         <v>1772</v>
       </c>
       <c r="B998" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B999" t="s">
         <v>1774</v>
@@ -14700,15 +14706,15 @@
         <v>1775</v>
       </c>
       <c r="B1000" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B1001" t="s">
         <v>1776</v>
-      </c>
-      <c r="B1001" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
@@ -14732,12 +14738,12 @@
         <v>1782</v>
       </c>
       <c r="B1004" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B1005" t="s">
         <v>1784</v>
@@ -14756,12 +14762,12 @@
         <v>1787</v>
       </c>
       <c r="B1007" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B1008" t="s">
         <v>1789</v>
@@ -14820,20 +14826,20 @@
         <v>1802</v>
       </c>
       <c r="B1015" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B1016" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B1017" t="s">
         <v>1805</v>
@@ -14852,12 +14858,12 @@
         <v>1808</v>
       </c>
       <c r="B1019" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1020" t="s">
         <v>1810</v>
@@ -14868,20 +14874,20 @@
         <v>1811</v>
       </c>
       <c r="B1021" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B1022" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B1023" t="s">
         <v>1814</v>
@@ -14916,20 +14922,20 @@
         <v>1821</v>
       </c>
       <c r="B1027" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1028" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B1029" t="s">
         <v>1824</v>
@@ -14948,12 +14954,12 @@
         <v>1827</v>
       </c>
       <c r="B1031" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1032" t="s">
         <v>1829</v>
@@ -15004,12 +15010,12 @@
         <v>1840</v>
       </c>
       <c r="B1038" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1039" t="s">
         <v>1842</v>
@@ -15044,12 +15050,12 @@
         <v>1849</v>
       </c>
       <c r="B1043" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B1044" t="s">
         <v>1851</v>
@@ -15060,12 +15066,12 @@
         <v>1852</v>
       </c>
       <c r="B1045" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B1046" t="s">
         <v>1854</v>
@@ -15084,12 +15090,12 @@
         <v>1857</v>
       </c>
       <c r="B1048" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1049" t="s">
         <v>1859</v>
@@ -15116,12 +15122,12 @@
         <v>1864</v>
       </c>
       <c r="B1052" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="B1053" t="s">
         <v>1866</v>
@@ -15268,12 +15274,12 @@
         <v>1901</v>
       </c>
       <c r="B1071" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B1072" t="s">
         <v>1903</v>
@@ -15348,12 +15354,12 @@
         <v>1920</v>
       </c>
       <c r="B1081" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1082" t="s">
         <v>1922</v>
@@ -15372,12 +15378,12 @@
         <v>1925</v>
       </c>
       <c r="B1084" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B1085" t="s">
         <v>1927</v>
@@ -15388,12 +15394,12 @@
         <v>1928</v>
       </c>
       <c r="B1086" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B1087" t="s">
         <v>1930</v>
@@ -15404,12 +15410,12 @@
         <v>1931</v>
       </c>
       <c r="B1088" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B1089" t="s">
         <v>1933</v>
@@ -15428,12 +15434,12 @@
         <v>1936</v>
       </c>
       <c r="B1091" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B1092" t="s">
         <v>1938</v>
@@ -15452,12 +15458,12 @@
         <v>1941</v>
       </c>
       <c r="B1094" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B1095" t="s">
         <v>1943</v>
@@ -15532,12 +15538,12 @@
         <v>1960</v>
       </c>
       <c r="B1104" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="B1105" t="s">
         <v>1962</v>
@@ -15612,12 +15618,12 @@
         <v>1979</v>
       </c>
       <c r="B1114" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B1115" t="s">
         <v>1981</v>
@@ -15628,20 +15634,20 @@
         <v>1982</v>
       </c>
       <c r="B1116" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B1117" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B1118" t="s">
         <v>1985</v>
@@ -15676,12 +15682,12 @@
         <v>1992</v>
       </c>
       <c r="B1122" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B1123" t="s">
         <v>1994</v>
@@ -15692,12 +15698,12 @@
         <v>1995</v>
       </c>
       <c r="B1124" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B1125" t="s">
         <v>1997</v>
@@ -15852,12 +15858,12 @@
         <v>2034</v>
       </c>
       <c r="B1144" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B1145" t="s">
         <v>2036</v>
@@ -15868,12 +15874,12 @@
         <v>2037</v>
       </c>
       <c r="B1146" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B1147" t="s">
         <v>2039</v>
@@ -15884,12 +15890,12 @@
         <v>2040</v>
       </c>
       <c r="B1148" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B1149" t="s">
         <v>2042</v>
@@ -15908,28 +15914,28 @@
         <v>2045</v>
       </c>
       <c r="B1151" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B1152" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="B1153" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B1154" t="s">
         <v>2049</v>
@@ -16012,12 +16018,12 @@
         <v>2068</v>
       </c>
       <c r="B1164" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="B1165" t="s">
         <v>2070</v>
@@ -16060,20 +16066,20 @@
         <v>2079</v>
       </c>
       <c r="B1170" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="B1171" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="B1172" t="s">
         <v>2082</v>
@@ -16108,12 +16114,12 @@
         <v>2089</v>
       </c>
       <c r="B1176" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="B1177" t="s">
         <v>2091</v>
@@ -16140,28 +16146,28 @@
         <v>2096</v>
       </c>
       <c r="B1180" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B1181" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B1182" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="B1183" t="s">
         <v>2100</v>
@@ -16180,12 +16186,12 @@
         <v>2103</v>
       </c>
       <c r="B1185" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="B1186" t="s">
         <v>2105</v>
@@ -16204,19 +16210,27 @@
         <v>2108</v>
       </c>
       <c r="B1188" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="B1189" t="s">
         <v>2110</v>
       </c>
     </row>
+    <row r="1190" spans="1:2">
+      <c r="A1190" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>2112</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1189"/>
+  <autoFilter ref="A1:B1190"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2115">
   <si>
     <t>en</t>
   </si>
@@ -374,6 +374,12 @@
   </si>
   <si>
     <t>Atgal į ateitį</t>
+  </si>
+  <si>
+    <t>Backrooms (Movie)</t>
+  </si>
+  <si>
+    <t>„Backrooms“ (filmas)</t>
   </si>
   <si>
     <t>Bag</t>
@@ -6702,7 +6708,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1190"/>
+  <dimension ref="A1:B1191"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -7258,12 +7264,12 @@
         <v>123</v>
       </c>
       <c r="B69" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B70" t="s">
         <v>125</v>
@@ -7282,36 +7288,36 @@
         <v>128</v>
       </c>
       <c r="B72" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B73" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B74" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B75" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B76" t="s">
         <v>133</v>
@@ -7322,12 +7328,12 @@
         <v>134</v>
       </c>
       <c r="B77" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B78" t="s">
         <v>136</v>
@@ -7362,12 +7368,12 @@
         <v>143</v>
       </c>
       <c r="B82" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B83" t="s">
         <v>145</v>
@@ -7434,20 +7440,20 @@
         <v>160</v>
       </c>
       <c r="B91" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B92" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B93" t="s">
         <v>163</v>
@@ -7466,12 +7472,12 @@
         <v>166</v>
       </c>
       <c r="B95" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B96" t="s">
         <v>168</v>
@@ -7482,28 +7488,28 @@
         <v>169</v>
       </c>
       <c r="B97" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B98" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B99" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B100" t="s">
         <v>173</v>
@@ -7554,12 +7560,12 @@
         <v>184</v>
       </c>
       <c r="B106" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B107" t="s">
         <v>186</v>
@@ -7602,20 +7608,20 @@
         <v>195</v>
       </c>
       <c r="B112" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B113" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B114" t="s">
         <v>198</v>
@@ -7634,12 +7640,12 @@
         <v>201</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B117" t="s">
         <v>203</v>
@@ -7682,28 +7688,28 @@
         <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B123" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B124" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B125" t="s">
         <v>216</v>
@@ -7754,12 +7760,12 @@
         <v>227</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B132" t="s">
         <v>229</v>
@@ -7770,12 +7776,12 @@
         <v>230</v>
       </c>
       <c r="B133" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B134" t="s">
         <v>232</v>
@@ -7810,12 +7816,12 @@
         <v>239</v>
       </c>
       <c r="B138" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B139" t="s">
         <v>241</v>
@@ -7930,12 +7936,12 @@
         <v>268</v>
       </c>
       <c r="B153" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B154" t="s">
         <v>270</v>
@@ -7986,12 +7992,12 @@
         <v>281</v>
       </c>
       <c r="B160" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B161" t="s">
         <v>283</v>
@@ -8122,12 +8128,12 @@
         <v>314</v>
       </c>
       <c r="B177" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B178" t="s">
         <v>316</v>
@@ -8138,12 +8144,12 @@
         <v>317</v>
       </c>
       <c r="B179" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B180" t="s">
         <v>319</v>
@@ -8354,12 +8360,12 @@
         <v>370</v>
       </c>
       <c r="B206" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B207" t="s">
         <v>372</v>
@@ -8378,20 +8384,20 @@
         <v>375</v>
       </c>
       <c r="B209" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B210" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B211" t="s">
         <v>378</v>
@@ -8434,12 +8440,12 @@
         <v>387</v>
       </c>
       <c r="B216" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B217" t="s">
         <v>389</v>
@@ -8458,12 +8464,12 @@
         <v>392</v>
       </c>
       <c r="B219" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B220" t="s">
         <v>394</v>
@@ -8474,12 +8480,12 @@
         <v>395</v>
       </c>
       <c r="B221" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B222" t="s">
         <v>397</v>
@@ -8490,20 +8496,20 @@
         <v>398</v>
       </c>
       <c r="B223" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B224" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B225" t="s">
         <v>401</v>
@@ -8538,12 +8544,12 @@
         <v>408</v>
       </c>
       <c r="B229" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B230" t="s">
         <v>410</v>
@@ -8562,12 +8568,12 @@
         <v>413</v>
       </c>
       <c r="B232" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B233" t="s">
         <v>415</v>
@@ -8594,12 +8600,12 @@
         <v>420</v>
       </c>
       <c r="B236" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B237" t="s">
         <v>422</v>
@@ -8666,12 +8672,12 @@
         <v>437</v>
       </c>
       <c r="B245" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B246" t="s">
         <v>439</v>
@@ -8706,12 +8712,12 @@
         <v>446</v>
       </c>
       <c r="B250" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B251" t="s">
         <v>448</v>
@@ -8722,12 +8728,12 @@
         <v>449</v>
       </c>
       <c r="B252" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B253" t="s">
         <v>451</v>
@@ -8738,20 +8744,20 @@
         <v>452</v>
       </c>
       <c r="B254" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B255" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B256" t="s">
         <v>455</v>
@@ -8762,12 +8768,12 @@
         <v>456</v>
       </c>
       <c r="B257" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B258" t="s">
         <v>458</v>
@@ -8834,20 +8840,20 @@
         <v>473</v>
       </c>
       <c r="B266" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B267" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B268" t="s">
         <v>476</v>
@@ -8866,28 +8872,28 @@
         <v>479</v>
       </c>
       <c r="B270" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B271" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B272" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B273" t="s">
         <v>483</v>
@@ -8914,20 +8920,20 @@
         <v>488</v>
       </c>
       <c r="B276" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B277" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B278" t="s">
         <v>491</v>
@@ -8970,20 +8976,20 @@
         <v>500</v>
       </c>
       <c r="B283" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B284" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B285" t="s">
         <v>503</v>
@@ -9002,12 +9008,12 @@
         <v>506</v>
       </c>
       <c r="B287" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B288" t="s">
         <v>508</v>
@@ -9034,12 +9040,12 @@
         <v>513</v>
       </c>
       <c r="B291" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B292" t="s">
         <v>515</v>
@@ -9074,20 +9080,20 @@
         <v>522</v>
       </c>
       <c r="B296" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B297" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B298" t="s">
         <v>525</v>
@@ -9138,12 +9144,12 @@
         <v>536</v>
       </c>
       <c r="B304" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B305" t="s">
         <v>538</v>
@@ -9162,12 +9168,12 @@
         <v>541</v>
       </c>
       <c r="B307" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B308" t="s">
         <v>543</v>
@@ -9186,20 +9192,20 @@
         <v>546</v>
       </c>
       <c r="B310" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B311" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B312" t="s">
         <v>549</v>
@@ -9218,20 +9224,20 @@
         <v>552</v>
       </c>
       <c r="B314" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B315" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B316" t="s">
         <v>555</v>
@@ -9266,12 +9272,12 @@
         <v>562</v>
       </c>
       <c r="B320" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B321" t="s">
         <v>564</v>
@@ -9282,12 +9288,12 @@
         <v>565</v>
       </c>
       <c r="B322" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B323" t="s">
         <v>567</v>
@@ -9322,12 +9328,12 @@
         <v>574</v>
       </c>
       <c r="B327" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B328" t="s">
         <v>576</v>
@@ -9370,12 +9376,12 @@
         <v>585</v>
       </c>
       <c r="B333" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B334" t="s">
         <v>587</v>
@@ -9442,12 +9448,12 @@
         <v>602</v>
       </c>
       <c r="B342" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B343" t="s">
         <v>604</v>
@@ -10178,28 +10184,28 @@
         <v>785</v>
       </c>
       <c r="B434" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B435" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B436" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B437" t="s">
         <v>789</v>
@@ -10298,12 +10304,12 @@
         <v>812</v>
       </c>
       <c r="B449" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B450" t="s">
         <v>814</v>
@@ -10314,12 +10320,12 @@
         <v>815</v>
       </c>
       <c r="B451" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B452" t="s">
         <v>817</v>
@@ -10434,12 +10440,12 @@
         <v>844</v>
       </c>
       <c r="B466" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B467" t="s">
         <v>846</v>
@@ -10450,20 +10456,20 @@
         <v>847</v>
       </c>
       <c r="B468" t="s">
-        <v>561</v>
+        <v>848</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B469" t="s">
-        <v>848</v>
+        <v>563</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B470" t="s">
         <v>850</v>
@@ -10474,12 +10480,12 @@
         <v>851</v>
       </c>
       <c r="B471" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B472" t="s">
         <v>853</v>
@@ -10498,23 +10504,23 @@
         <v>856</v>
       </c>
       <c r="B474" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B475" t="s">
-        <v>561</v>
+        <v>858</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B476" t="s">
-        <v>859</v>
+        <v>563</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -10522,12 +10528,12 @@
         <v>860</v>
       </c>
       <c r="B477" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B478" t="s">
         <v>862</v>
@@ -10578,20 +10584,20 @@
         <v>873</v>
       </c>
       <c r="B484" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B485" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B486" t="s">
         <v>876</v>
@@ -10602,12 +10608,12 @@
         <v>877</v>
       </c>
       <c r="B487" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B488" t="s">
         <v>879</v>
@@ -10618,28 +10624,28 @@
         <v>880</v>
       </c>
       <c r="B489" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B490" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B491" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B492" t="s">
         <v>884</v>
@@ -10826,12 +10832,12 @@
         <v>929</v>
       </c>
       <c r="B515" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B516" t="s">
         <v>931</v>
@@ -10978,12 +10984,12 @@
         <v>966</v>
       </c>
       <c r="B534" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B535" t="s">
         <v>968</v>
@@ -11002,20 +11008,20 @@
         <v>971</v>
       </c>
       <c r="B537" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B538" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B539" t="s">
         <v>974</v>
@@ -11034,28 +11040,28 @@
         <v>977</v>
       </c>
       <c r="B541" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B542" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B543" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B544" t="s">
         <v>981</v>
@@ -11090,20 +11096,20 @@
         <v>988</v>
       </c>
       <c r="B548" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B549" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B550" t="s">
         <v>991</v>
@@ -11114,12 +11120,12 @@
         <v>992</v>
       </c>
       <c r="B551" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B552" t="s">
         <v>994</v>
@@ -11130,12 +11136,12 @@
         <v>995</v>
       </c>
       <c r="B553" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B554" t="s">
         <v>997</v>
@@ -11234,12 +11240,12 @@
         <v>1020</v>
       </c>
       <c r="B566" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B567" t="s">
         <v>1022</v>
@@ -11266,12 +11272,12 @@
         <v>1027</v>
       </c>
       <c r="B570" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B571" t="s">
         <v>1029</v>
@@ -11322,12 +11328,12 @@
         <v>1040</v>
       </c>
       <c r="B577" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B578" t="s">
         <v>1042</v>
@@ -11338,28 +11344,28 @@
         <v>1043</v>
       </c>
       <c r="B579" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B580" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B581" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B582" t="s">
         <v>1047</v>
@@ -11506,12 +11512,12 @@
         <v>1082</v>
       </c>
       <c r="B600" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B601" t="s">
         <v>1084</v>
@@ -11578,28 +11584,28 @@
         <v>1099</v>
       </c>
       <c r="B609" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B610" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B611" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B612" t="s">
         <v>1103</v>
@@ -11730,12 +11736,12 @@
         <v>1134</v>
       </c>
       <c r="B628" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B629" t="s">
         <v>1136</v>
@@ -11754,12 +11760,12 @@
         <v>1139</v>
       </c>
       <c r="B631" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B632" t="s">
         <v>1141</v>
@@ -11794,12 +11800,12 @@
         <v>1148</v>
       </c>
       <c r="B636" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B637" t="s">
         <v>1150</v>
@@ -11810,12 +11816,12 @@
         <v>1151</v>
       </c>
       <c r="B638" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B639" t="s">
         <v>1153</v>
@@ -11834,52 +11840,52 @@
         <v>1156</v>
       </c>
       <c r="B641" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B642" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B643" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B644" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B645" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B646" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B647" t="s">
         <v>1163</v>
@@ -11890,36 +11896,36 @@
         <v>1164</v>
       </c>
       <c r="B648" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B649" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B650" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B651" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B652" t="s">
         <v>1169</v>
@@ -11954,28 +11960,28 @@
         <v>1176</v>
       </c>
       <c r="B656" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B657" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B658" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B659" t="s">
         <v>1180</v>
@@ -11986,12 +11992,12 @@
         <v>1181</v>
       </c>
       <c r="B660" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B661" t="s">
         <v>1183</v>
@@ -12186,12 +12192,12 @@
         <v>1230</v>
       </c>
       <c r="B685" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B686" t="s">
         <v>1232</v>
@@ -12218,20 +12224,20 @@
         <v>1237</v>
       </c>
       <c r="B689" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B690" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B691" t="s">
         <v>1240</v>
@@ -12362,12 +12368,12 @@
         <v>1271</v>
       </c>
       <c r="B707" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B708" t="s">
         <v>1273</v>
@@ -12378,20 +12384,20 @@
         <v>1274</v>
       </c>
       <c r="B709" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B710" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B711" t="s">
         <v>1277</v>
@@ -12402,28 +12408,28 @@
         <v>1278</v>
       </c>
       <c r="B712" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B713" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B714" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B715" t="s">
         <v>1282</v>
@@ -12442,20 +12448,20 @@
         <v>1285</v>
       </c>
       <c r="B717" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B718" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B719" t="s">
         <v>1288</v>
@@ -12554,20 +12560,20 @@
         <v>1311</v>
       </c>
       <c r="B731" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B732" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B733" t="s">
         <v>1314</v>
@@ -12610,12 +12616,12 @@
         <v>1323</v>
       </c>
       <c r="B738" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B739" t="s">
         <v>1325</v>
@@ -12666,12 +12672,12 @@
         <v>1336</v>
       </c>
       <c r="B745" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B746" t="s">
         <v>1338</v>
@@ -12698,20 +12704,20 @@
         <v>1343</v>
       </c>
       <c r="B749" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B750" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B751" t="s">
         <v>1346</v>
@@ -12730,20 +12736,20 @@
         <v>1349</v>
       </c>
       <c r="B753" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B754" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B755" t="s">
         <v>1352</v>
@@ -12850,28 +12856,28 @@
         <v>1377</v>
       </c>
       <c r="B768" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B769" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B770" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B771" t="s">
         <v>1381</v>
@@ -12914,12 +12920,12 @@
         <v>1390</v>
       </c>
       <c r="B776" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B777" t="s">
         <v>1392</v>
@@ -13026,28 +13032,28 @@
         <v>1417</v>
       </c>
       <c r="B790" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B791" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B792" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B793" t="s">
         <v>1421</v>
@@ -13066,12 +13072,12 @@
         <v>1424</v>
       </c>
       <c r="B795" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B796" t="s">
         <v>1426</v>
@@ -13090,12 +13096,12 @@
         <v>1429</v>
       </c>
       <c r="B798" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B799" t="s">
         <v>1431</v>
@@ -13114,28 +13120,28 @@
         <v>1434</v>
       </c>
       <c r="B801" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B802" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B803" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B804" t="s">
         <v>1438</v>
@@ -13146,20 +13152,20 @@
         <v>1439</v>
       </c>
       <c r="B805" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B806" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B807" t="s">
         <v>1442</v>
@@ -13226,20 +13232,20 @@
         <v>1457</v>
       </c>
       <c r="B815" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B816" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B817" t="s">
         <v>1460</v>
@@ -13274,12 +13280,12 @@
         <v>1467</v>
       </c>
       <c r="B821" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B822" t="s">
         <v>1469</v>
@@ -13298,12 +13304,12 @@
         <v>1472</v>
       </c>
       <c r="B824" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B825" t="s">
         <v>1474</v>
@@ -13322,12 +13328,12 @@
         <v>1477</v>
       </c>
       <c r="B827" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B828" t="s">
         <v>1479</v>
@@ -13354,12 +13360,12 @@
         <v>1484</v>
       </c>
       <c r="B831" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B832" t="s">
         <v>1486</v>
@@ -13370,12 +13376,12 @@
         <v>1487</v>
       </c>
       <c r="B833" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B834" t="s">
         <v>1489</v>
@@ -13418,36 +13424,36 @@
         <v>1498</v>
       </c>
       <c r="B839" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B840" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B841" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B842" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B843" t="s">
         <v>1503</v>
@@ -13514,28 +13520,28 @@
         <v>1518</v>
       </c>
       <c r="B851" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B852" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B853" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B854" t="s">
         <v>1522</v>
@@ -13642,20 +13648,20 @@
         <v>1547</v>
       </c>
       <c r="B867" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B868" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B869" t="s">
         <v>1550</v>
@@ -13674,12 +13680,12 @@
         <v>1553</v>
       </c>
       <c r="B871" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B872" t="s">
         <v>1555</v>
@@ -13690,12 +13696,12 @@
         <v>1556</v>
       </c>
       <c r="B873" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B874" t="s">
         <v>1558</v>
@@ -13818,20 +13824,20 @@
         <v>1587</v>
       </c>
       <c r="B889" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B890" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B891" t="s">
         <v>1590</v>
@@ -13858,12 +13864,12 @@
         <v>1595</v>
       </c>
       <c r="B894" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B895" t="s">
         <v>1597</v>
@@ -13882,12 +13888,12 @@
         <v>1600</v>
       </c>
       <c r="B897" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B898" t="s">
         <v>1602</v>
@@ -13898,12 +13904,12 @@
         <v>1603</v>
       </c>
       <c r="B899" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B900" t="s">
         <v>1605</v>
@@ -13914,12 +13920,12 @@
         <v>1606</v>
       </c>
       <c r="B901" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B902" t="s">
         <v>1608</v>
@@ -13930,12 +13936,12 @@
         <v>1609</v>
       </c>
       <c r="B903" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B904" t="s">
         <v>1611</v>
@@ -13994,12 +14000,12 @@
         <v>1624</v>
       </c>
       <c r="B911" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B912" t="s">
         <v>1626</v>
@@ -14026,12 +14032,12 @@
         <v>1631</v>
       </c>
       <c r="B915" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B916" t="s">
         <v>1633</v>
@@ -14042,20 +14048,20 @@
         <v>1634</v>
       </c>
       <c r="B917" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B918" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B919" t="s">
         <v>1637</v>
@@ -14066,12 +14072,12 @@
         <v>1638</v>
       </c>
       <c r="B920" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B921" t="s">
         <v>1640</v>
@@ -14106,28 +14112,28 @@
         <v>1647</v>
       </c>
       <c r="B925" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B926" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B927" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B928" t="s">
         <v>1651</v>
@@ -14170,20 +14176,20 @@
         <v>1660</v>
       </c>
       <c r="B933" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B934" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B935" t="s">
         <v>1663</v>
@@ -14218,12 +14224,12 @@
         <v>1670</v>
       </c>
       <c r="B939" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B940" t="s">
         <v>1672</v>
@@ -14234,20 +14240,20 @@
         <v>1673</v>
       </c>
       <c r="B941" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B942" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B943" t="s">
         <v>1676</v>
@@ -14338,20 +14344,20 @@
         <v>1697</v>
       </c>
       <c r="B954" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B955" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B956" t="s">
         <v>1700</v>
@@ -14370,12 +14376,12 @@
         <v>1703</v>
       </c>
       <c r="B958" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B959" t="s">
         <v>1705</v>
@@ -14386,28 +14392,28 @@
         <v>1706</v>
       </c>
       <c r="B960" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B961" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B962" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B963" t="s">
         <v>1710</v>
@@ -14450,20 +14456,20 @@
         <v>1719</v>
       </c>
       <c r="B968" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B969" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B970" t="s">
         <v>1722</v>
@@ -14522,20 +14528,20 @@
         <v>1735</v>
       </c>
       <c r="B977" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B978" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B979" t="s">
         <v>1738</v>
@@ -14634,20 +14640,20 @@
         <v>1761</v>
       </c>
       <c r="B991" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B992" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B993" t="s">
         <v>1764</v>
@@ -14682,12 +14688,12 @@
         <v>1771</v>
       </c>
       <c r="B997" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B998" t="s">
         <v>1773</v>
@@ -14698,12 +14704,12 @@
         <v>1774</v>
       </c>
       <c r="B999" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B1000" t="s">
         <v>1776</v>
@@ -14714,15 +14720,15 @@
         <v>1777</v>
       </c>
       <c r="B1001" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1002" t="s">
         <v>1778</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>1779</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
@@ -14746,12 +14752,12 @@
         <v>1784</v>
       </c>
       <c r="B1005" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B1006" t="s">
         <v>1786</v>
@@ -14770,12 +14776,12 @@
         <v>1789</v>
       </c>
       <c r="B1008" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B1009" t="s">
         <v>1791</v>
@@ -14834,20 +14840,20 @@
         <v>1804</v>
       </c>
       <c r="B1016" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B1017" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B1018" t="s">
         <v>1807</v>
@@ -14866,12 +14872,12 @@
         <v>1810</v>
       </c>
       <c r="B1020" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1021" t="s">
         <v>1812</v>
@@ -14882,20 +14888,20 @@
         <v>1813</v>
       </c>
       <c r="B1022" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B1023" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1024" t="s">
         <v>1816</v>
@@ -14930,20 +14936,20 @@
         <v>1823</v>
       </c>
       <c r="B1028" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1029" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B1030" t="s">
         <v>1826</v>
@@ -14962,12 +14968,12 @@
         <v>1829</v>
       </c>
       <c r="B1032" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B1033" t="s">
         <v>1831</v>
@@ -15018,12 +15024,12 @@
         <v>1842</v>
       </c>
       <c r="B1039" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B1040" t="s">
         <v>1844</v>
@@ -15058,12 +15064,12 @@
         <v>1851</v>
       </c>
       <c r="B1044" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B1045" t="s">
         <v>1853</v>
@@ -15074,12 +15080,12 @@
         <v>1854</v>
       </c>
       <c r="B1046" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B1047" t="s">
         <v>1856</v>
@@ -15098,12 +15104,12 @@
         <v>1859</v>
       </c>
       <c r="B1049" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1050" t="s">
         <v>1861</v>
@@ -15130,12 +15136,12 @@
         <v>1866</v>
       </c>
       <c r="B1053" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B1054" t="s">
         <v>1868</v>
@@ -15282,12 +15288,12 @@
         <v>1903</v>
       </c>
       <c r="B1072" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1073" t="s">
         <v>1905</v>
@@ -15362,12 +15368,12 @@
         <v>1922</v>
       </c>
       <c r="B1082" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1083" t="s">
         <v>1924</v>
@@ -15386,12 +15392,12 @@
         <v>1927</v>
       </c>
       <c r="B1085" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="B1086" t="s">
         <v>1929</v>
@@ -15402,12 +15408,12 @@
         <v>1930</v>
       </c>
       <c r="B1087" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B1088" t="s">
         <v>1932</v>
@@ -15418,12 +15424,12 @@
         <v>1933</v>
       </c>
       <c r="B1089" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B1090" t="s">
         <v>1935</v>
@@ -15442,12 +15448,12 @@
         <v>1938</v>
       </c>
       <c r="B1092" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B1093" t="s">
         <v>1940</v>
@@ -15466,12 +15472,12 @@
         <v>1943</v>
       </c>
       <c r="B1095" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B1096" t="s">
         <v>1945</v>
@@ -15546,12 +15552,12 @@
         <v>1962</v>
       </c>
       <c r="B1105" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B1106" t="s">
         <v>1964</v>
@@ -15626,12 +15632,12 @@
         <v>1981</v>
       </c>
       <c r="B1115" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B1116" t="s">
         <v>1983</v>
@@ -15642,20 +15648,20 @@
         <v>1984</v>
       </c>
       <c r="B1117" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B1118" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B1119" t="s">
         <v>1987</v>
@@ -15690,12 +15696,12 @@
         <v>1994</v>
       </c>
       <c r="B1123" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B1124" t="s">
         <v>1996</v>
@@ -15706,12 +15712,12 @@
         <v>1997</v>
       </c>
       <c r="B1125" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="B1126" t="s">
         <v>1999</v>
@@ -15866,12 +15872,12 @@
         <v>2036</v>
       </c>
       <c r="B1145" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B1146" t="s">
         <v>2038</v>
@@ -15882,12 +15888,12 @@
         <v>2039</v>
       </c>
       <c r="B1147" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="B1148" t="s">
         <v>2041</v>
@@ -15898,12 +15904,12 @@
         <v>2042</v>
       </c>
       <c r="B1149" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="B1150" t="s">
         <v>2044</v>
@@ -15922,28 +15928,28 @@
         <v>2047</v>
       </c>
       <c r="B1152" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B1153" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B1154" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="B1155" t="s">
         <v>2051</v>
@@ -16026,12 +16032,12 @@
         <v>2070</v>
       </c>
       <c r="B1165" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="B1166" t="s">
         <v>2072</v>
@@ -16074,20 +16080,20 @@
         <v>2081</v>
       </c>
       <c r="B1171" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="B1172" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="B1173" t="s">
         <v>2084</v>
@@ -16122,12 +16128,12 @@
         <v>2091</v>
       </c>
       <c r="B1177" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="B1178" t="s">
         <v>2093</v>
@@ -16154,28 +16160,28 @@
         <v>2098</v>
       </c>
       <c r="B1181" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="B1182" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B1183" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B1184" t="s">
         <v>2102</v>
@@ -16194,12 +16200,12 @@
         <v>2105</v>
       </c>
       <c r="B1186" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="B1187" t="s">
         <v>2107</v>
@@ -16218,19 +16224,27 @@
         <v>2110</v>
       </c>
       <c r="B1189" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="B1190" t="s">
         <v>2112</v>
       </c>
     </row>
+    <row r="1191" spans="1:2">
+      <c r="A1191" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>2114</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1190"/>
+  <autoFilter ref="A1:B1191"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2117">
   <si>
     <t>en</t>
   </si>
@@ -1382,6 +1382,12 @@
   </si>
   <si>
     <t>Diablo</t>
+  </si>
+  <si>
+    <t>Die of Death</t>
+  </si>
+  <si>
+    <t>Mirties kauliukas</t>
   </si>
   <si>
     <t>Digimon</t>
@@ -6708,7 +6714,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1191"/>
+  <dimension ref="A1:B1192"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -8760,12 +8766,12 @@
         <v>455</v>
       </c>
       <c r="B256" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B257" t="s">
         <v>457</v>
@@ -8776,12 +8782,12 @@
         <v>458</v>
       </c>
       <c r="B258" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B259" t="s">
         <v>460</v>
@@ -8848,20 +8854,20 @@
         <v>475</v>
       </c>
       <c r="B267" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B268" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B269" t="s">
         <v>478</v>
@@ -8880,28 +8886,28 @@
         <v>481</v>
       </c>
       <c r="B271" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B272" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B273" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B274" t="s">
         <v>485</v>
@@ -8928,20 +8934,20 @@
         <v>490</v>
       </c>
       <c r="B277" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B278" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B279" t="s">
         <v>493</v>
@@ -8984,20 +8990,20 @@
         <v>502</v>
       </c>
       <c r="B284" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B285" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B286" t="s">
         <v>505</v>
@@ -9016,12 +9022,12 @@
         <v>508</v>
       </c>
       <c r="B288" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B289" t="s">
         <v>510</v>
@@ -9048,12 +9054,12 @@
         <v>515</v>
       </c>
       <c r="B292" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B293" t="s">
         <v>517</v>
@@ -9088,20 +9094,20 @@
         <v>524</v>
       </c>
       <c r="B297" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B298" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B299" t="s">
         <v>527</v>
@@ -9152,12 +9158,12 @@
         <v>538</v>
       </c>
       <c r="B305" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B306" t="s">
         <v>540</v>
@@ -9176,12 +9182,12 @@
         <v>543</v>
       </c>
       <c r="B308" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B309" t="s">
         <v>545</v>
@@ -9200,20 +9206,20 @@
         <v>548</v>
       </c>
       <c r="B311" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B312" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B313" t="s">
         <v>551</v>
@@ -9232,20 +9238,20 @@
         <v>554</v>
       </c>
       <c r="B315" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B316" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B317" t="s">
         <v>557</v>
@@ -9280,12 +9286,12 @@
         <v>564</v>
       </c>
       <c r="B321" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B322" t="s">
         <v>566</v>
@@ -9296,12 +9302,12 @@
         <v>567</v>
       </c>
       <c r="B323" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B324" t="s">
         <v>569</v>
@@ -9336,12 +9342,12 @@
         <v>576</v>
       </c>
       <c r="B328" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B329" t="s">
         <v>578</v>
@@ -9384,12 +9390,12 @@
         <v>587</v>
       </c>
       <c r="B334" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B335" t="s">
         <v>589</v>
@@ -9456,12 +9462,12 @@
         <v>604</v>
       </c>
       <c r="B343" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B344" t="s">
         <v>606</v>
@@ -10192,28 +10198,28 @@
         <v>787</v>
       </c>
       <c r="B435" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B436" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B437" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B438" t="s">
         <v>791</v>
@@ -10312,12 +10318,12 @@
         <v>814</v>
       </c>
       <c r="B450" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B451" t="s">
         <v>816</v>
@@ -10328,12 +10334,12 @@
         <v>817</v>
       </c>
       <c r="B452" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B453" t="s">
         <v>819</v>
@@ -10448,12 +10454,12 @@
         <v>846</v>
       </c>
       <c r="B467" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B468" t="s">
         <v>848</v>
@@ -10464,20 +10470,20 @@
         <v>849</v>
       </c>
       <c r="B469" t="s">
-        <v>563</v>
+        <v>850</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B470" t="s">
-        <v>850</v>
+        <v>565</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B471" t="s">
         <v>852</v>
@@ -10488,12 +10494,12 @@
         <v>853</v>
       </c>
       <c r="B472" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B473" t="s">
         <v>855</v>
@@ -10512,23 +10518,23 @@
         <v>858</v>
       </c>
       <c r="B475" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B476" t="s">
-        <v>563</v>
+        <v>860</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B477" t="s">
-        <v>861</v>
+        <v>565</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -10536,12 +10542,12 @@
         <v>862</v>
       </c>
       <c r="B478" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B479" t="s">
         <v>864</v>
@@ -10592,20 +10598,20 @@
         <v>875</v>
       </c>
       <c r="B485" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B486" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B487" t="s">
         <v>878</v>
@@ -10616,12 +10622,12 @@
         <v>879</v>
       </c>
       <c r="B488" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B489" t="s">
         <v>881</v>
@@ -10632,28 +10638,28 @@
         <v>882</v>
       </c>
       <c r="B490" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B491" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B492" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B493" t="s">
         <v>886</v>
@@ -10840,12 +10846,12 @@
         <v>931</v>
       </c>
       <c r="B516" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B517" t="s">
         <v>933</v>
@@ -10992,12 +10998,12 @@
         <v>968</v>
       </c>
       <c r="B535" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B536" t="s">
         <v>970</v>
@@ -11016,20 +11022,20 @@
         <v>973</v>
       </c>
       <c r="B538" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B539" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B540" t="s">
         <v>976</v>
@@ -11048,28 +11054,28 @@
         <v>979</v>
       </c>
       <c r="B542" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B543" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B544" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B545" t="s">
         <v>983</v>
@@ -11104,20 +11110,20 @@
         <v>990</v>
       </c>
       <c r="B549" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B550" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B551" t="s">
         <v>993</v>
@@ -11128,12 +11134,12 @@
         <v>994</v>
       </c>
       <c r="B552" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B553" t="s">
         <v>996</v>
@@ -11144,12 +11150,12 @@
         <v>997</v>
       </c>
       <c r="B554" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B555" t="s">
         <v>999</v>
@@ -11248,12 +11254,12 @@
         <v>1022</v>
       </c>
       <c r="B567" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B568" t="s">
         <v>1024</v>
@@ -11280,12 +11286,12 @@
         <v>1029</v>
       </c>
       <c r="B571" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B572" t="s">
         <v>1031</v>
@@ -11336,12 +11342,12 @@
         <v>1042</v>
       </c>
       <c r="B578" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B579" t="s">
         <v>1044</v>
@@ -11352,28 +11358,28 @@
         <v>1045</v>
       </c>
       <c r="B580" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B581" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B582" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B583" t="s">
         <v>1049</v>
@@ -11520,12 +11526,12 @@
         <v>1084</v>
       </c>
       <c r="B601" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B602" t="s">
         <v>1086</v>
@@ -11592,28 +11598,28 @@
         <v>1101</v>
       </c>
       <c r="B610" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B611" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B612" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B613" t="s">
         <v>1105</v>
@@ -11744,12 +11750,12 @@
         <v>1136</v>
       </c>
       <c r="B629" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B630" t="s">
         <v>1138</v>
@@ -11768,12 +11774,12 @@
         <v>1141</v>
       </c>
       <c r="B632" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B633" t="s">
         <v>1143</v>
@@ -11808,12 +11814,12 @@
         <v>1150</v>
       </c>
       <c r="B637" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B638" t="s">
         <v>1152</v>
@@ -11824,12 +11830,12 @@
         <v>1153</v>
       </c>
       <c r="B639" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B640" t="s">
         <v>1155</v>
@@ -11848,52 +11854,52 @@
         <v>1158</v>
       </c>
       <c r="B642" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B643" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B644" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B645" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B646" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B647" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B648" t="s">
         <v>1165</v>
@@ -11904,36 +11910,36 @@
         <v>1166</v>
       </c>
       <c r="B649" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B650" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B651" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B652" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B653" t="s">
         <v>1171</v>
@@ -11968,28 +11974,28 @@
         <v>1178</v>
       </c>
       <c r="B657" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B658" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B659" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B660" t="s">
         <v>1182</v>
@@ -12000,12 +12006,12 @@
         <v>1183</v>
       </c>
       <c r="B661" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B662" t="s">
         <v>1185</v>
@@ -12200,12 +12206,12 @@
         <v>1232</v>
       </c>
       <c r="B686" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B687" t="s">
         <v>1234</v>
@@ -12232,20 +12238,20 @@
         <v>1239</v>
       </c>
       <c r="B690" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B691" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B692" t="s">
         <v>1242</v>
@@ -12376,12 +12382,12 @@
         <v>1273</v>
       </c>
       <c r="B708" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B709" t="s">
         <v>1275</v>
@@ -12392,20 +12398,20 @@
         <v>1276</v>
       </c>
       <c r="B710" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B711" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B712" t="s">
         <v>1279</v>
@@ -12416,28 +12422,28 @@
         <v>1280</v>
       </c>
       <c r="B713" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B714" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B715" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B716" t="s">
         <v>1284</v>
@@ -12456,20 +12462,20 @@
         <v>1287</v>
       </c>
       <c r="B718" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B719" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B720" t="s">
         <v>1290</v>
@@ -12568,20 +12574,20 @@
         <v>1313</v>
       </c>
       <c r="B732" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B733" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B734" t="s">
         <v>1316</v>
@@ -12624,12 +12630,12 @@
         <v>1325</v>
       </c>
       <c r="B739" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B740" t="s">
         <v>1327</v>
@@ -12680,12 +12686,12 @@
         <v>1338</v>
       </c>
       <c r="B746" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B747" t="s">
         <v>1340</v>
@@ -12712,20 +12718,20 @@
         <v>1345</v>
       </c>
       <c r="B750" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B751" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B752" t="s">
         <v>1348</v>
@@ -12744,20 +12750,20 @@
         <v>1351</v>
       </c>
       <c r="B754" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B755" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B756" t="s">
         <v>1354</v>
@@ -12864,28 +12870,28 @@
         <v>1379</v>
       </c>
       <c r="B769" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B770" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B771" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B772" t="s">
         <v>1383</v>
@@ -12928,12 +12934,12 @@
         <v>1392</v>
       </c>
       <c r="B777" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B778" t="s">
         <v>1394</v>
@@ -13040,28 +13046,28 @@
         <v>1419</v>
       </c>
       <c r="B791" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B792" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B793" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B794" t="s">
         <v>1423</v>
@@ -13080,12 +13086,12 @@
         <v>1426</v>
       </c>
       <c r="B796" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B797" t="s">
         <v>1428</v>
@@ -13104,12 +13110,12 @@
         <v>1431</v>
       </c>
       <c r="B799" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B800" t="s">
         <v>1433</v>
@@ -13128,28 +13134,28 @@
         <v>1436</v>
       </c>
       <c r="B802" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B803" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B804" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B805" t="s">
         <v>1440</v>
@@ -13160,20 +13166,20 @@
         <v>1441</v>
       </c>
       <c r="B806" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B807" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B808" t="s">
         <v>1444</v>
@@ -13240,20 +13246,20 @@
         <v>1459</v>
       </c>
       <c r="B816" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B817" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B818" t="s">
         <v>1462</v>
@@ -13288,12 +13294,12 @@
         <v>1469</v>
       </c>
       <c r="B822" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B823" t="s">
         <v>1471</v>
@@ -13312,12 +13318,12 @@
         <v>1474</v>
       </c>
       <c r="B825" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B826" t="s">
         <v>1476</v>
@@ -13336,12 +13342,12 @@
         <v>1479</v>
       </c>
       <c r="B828" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B829" t="s">
         <v>1481</v>
@@ -13368,12 +13374,12 @@
         <v>1486</v>
       </c>
       <c r="B832" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B833" t="s">
         <v>1488</v>
@@ -13384,12 +13390,12 @@
         <v>1489</v>
       </c>
       <c r="B834" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B835" t="s">
         <v>1491</v>
@@ -13432,36 +13438,36 @@
         <v>1500</v>
       </c>
       <c r="B840" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B841" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B842" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B843" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B844" t="s">
         <v>1505</v>
@@ -13528,28 +13534,28 @@
         <v>1520</v>
       </c>
       <c r="B852" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B853" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B854" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B855" t="s">
         <v>1524</v>
@@ -13656,20 +13662,20 @@
         <v>1549</v>
       </c>
       <c r="B868" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B869" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B870" t="s">
         <v>1552</v>
@@ -13688,12 +13694,12 @@
         <v>1555</v>
       </c>
       <c r="B872" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B873" t="s">
         <v>1557</v>
@@ -13704,12 +13710,12 @@
         <v>1558</v>
       </c>
       <c r="B874" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B875" t="s">
         <v>1560</v>
@@ -13832,20 +13838,20 @@
         <v>1589</v>
       </c>
       <c r="B890" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B891" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B892" t="s">
         <v>1592</v>
@@ -13872,12 +13878,12 @@
         <v>1597</v>
       </c>
       <c r="B895" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B896" t="s">
         <v>1599</v>
@@ -13896,12 +13902,12 @@
         <v>1602</v>
       </c>
       <c r="B898" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B899" t="s">
         <v>1604</v>
@@ -13912,12 +13918,12 @@
         <v>1605</v>
       </c>
       <c r="B900" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B901" t="s">
         <v>1607</v>
@@ -13928,12 +13934,12 @@
         <v>1608</v>
       </c>
       <c r="B902" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B903" t="s">
         <v>1610</v>
@@ -13944,12 +13950,12 @@
         <v>1611</v>
       </c>
       <c r="B904" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B905" t="s">
         <v>1613</v>
@@ -14008,12 +14014,12 @@
         <v>1626</v>
       </c>
       <c r="B912" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B913" t="s">
         <v>1628</v>
@@ -14040,12 +14046,12 @@
         <v>1633</v>
       </c>
       <c r="B916" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B917" t="s">
         <v>1635</v>
@@ -14056,20 +14062,20 @@
         <v>1636</v>
       </c>
       <c r="B918" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B919" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B920" t="s">
         <v>1639</v>
@@ -14080,12 +14086,12 @@
         <v>1640</v>
       </c>
       <c r="B921" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B922" t="s">
         <v>1642</v>
@@ -14120,28 +14126,28 @@
         <v>1649</v>
       </c>
       <c r="B926" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B927" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B928" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B929" t="s">
         <v>1653</v>
@@ -14184,20 +14190,20 @@
         <v>1662</v>
       </c>
       <c r="B934" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B935" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B936" t="s">
         <v>1665</v>
@@ -14232,12 +14238,12 @@
         <v>1672</v>
       </c>
       <c r="B940" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B941" t="s">
         <v>1674</v>
@@ -14248,20 +14254,20 @@
         <v>1675</v>
       </c>
       <c r="B942" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B943" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B944" t="s">
         <v>1678</v>
@@ -14352,20 +14358,20 @@
         <v>1699</v>
       </c>
       <c r="B955" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B956" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B957" t="s">
         <v>1702</v>
@@ -14384,12 +14390,12 @@
         <v>1705</v>
       </c>
       <c r="B959" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B960" t="s">
         <v>1707</v>
@@ -14400,28 +14406,28 @@
         <v>1708</v>
       </c>
       <c r="B961" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B962" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B963" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B964" t="s">
         <v>1712</v>
@@ -14464,20 +14470,20 @@
         <v>1721</v>
       </c>
       <c r="B969" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B970" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B971" t="s">
         <v>1724</v>
@@ -14536,20 +14542,20 @@
         <v>1737</v>
       </c>
       <c r="B978" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B979" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B980" t="s">
         <v>1740</v>
@@ -14648,20 +14654,20 @@
         <v>1763</v>
       </c>
       <c r="B992" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B993" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B994" t="s">
         <v>1766</v>
@@ -14696,12 +14702,12 @@
         <v>1773</v>
       </c>
       <c r="B998" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B999" t="s">
         <v>1775</v>
@@ -14712,12 +14718,12 @@
         <v>1776</v>
       </c>
       <c r="B1000" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1001" t="s">
         <v>1778</v>
@@ -14728,15 +14734,15 @@
         <v>1779</v>
       </c>
       <c r="B1002" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B1003" t="s">
         <v>1780</v>
-      </c>
-      <c r="B1003" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
@@ -14760,12 +14766,12 @@
         <v>1786</v>
       </c>
       <c r="B1006" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B1007" t="s">
         <v>1788</v>
@@ -14784,12 +14790,12 @@
         <v>1791</v>
       </c>
       <c r="B1009" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1010" t="s">
         <v>1793</v>
@@ -14848,20 +14854,20 @@
         <v>1806</v>
       </c>
       <c r="B1017" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B1018" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1019" t="s">
         <v>1809</v>
@@ -14880,12 +14886,12 @@
         <v>1812</v>
       </c>
       <c r="B1021" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B1022" t="s">
         <v>1814</v>
@@ -14896,20 +14902,20 @@
         <v>1815</v>
       </c>
       <c r="B1023" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B1024" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B1025" t="s">
         <v>1818</v>
@@ -14944,20 +14950,20 @@
         <v>1825</v>
       </c>
       <c r="B1029" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1030" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B1031" t="s">
         <v>1828</v>
@@ -14976,12 +14982,12 @@
         <v>1831</v>
       </c>
       <c r="B1033" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1034" t="s">
         <v>1833</v>
@@ -15032,12 +15038,12 @@
         <v>1844</v>
       </c>
       <c r="B1040" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B1041" t="s">
         <v>1846</v>
@@ -15072,12 +15078,12 @@
         <v>1853</v>
       </c>
       <c r="B1045" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1046" t="s">
         <v>1855</v>
@@ -15088,12 +15094,12 @@
         <v>1856</v>
       </c>
       <c r="B1047" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B1048" t="s">
         <v>1858</v>
@@ -15112,12 +15118,12 @@
         <v>1861</v>
       </c>
       <c r="B1050" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1051" t="s">
         <v>1863</v>
@@ -15144,12 +15150,12 @@
         <v>1868</v>
       </c>
       <c r="B1054" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B1055" t="s">
         <v>1870</v>
@@ -15296,12 +15302,12 @@
         <v>1905</v>
       </c>
       <c r="B1073" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1074" t="s">
         <v>1907</v>
@@ -15376,12 +15382,12 @@
         <v>1924</v>
       </c>
       <c r="B1083" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1084" t="s">
         <v>1926</v>
@@ -15400,12 +15406,12 @@
         <v>1929</v>
       </c>
       <c r="B1086" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1087" t="s">
         <v>1931</v>
@@ -15416,12 +15422,12 @@
         <v>1932</v>
       </c>
       <c r="B1088" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1089" t="s">
         <v>1934</v>
@@ -15432,12 +15438,12 @@
         <v>1935</v>
       </c>
       <c r="B1090" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="B1091" t="s">
         <v>1937</v>
@@ -15456,12 +15462,12 @@
         <v>1940</v>
       </c>
       <c r="B1093" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B1094" t="s">
         <v>1942</v>
@@ -15480,12 +15486,12 @@
         <v>1945</v>
       </c>
       <c r="B1096" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B1097" t="s">
         <v>1947</v>
@@ -15560,12 +15566,12 @@
         <v>1964</v>
       </c>
       <c r="B1106" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B1107" t="s">
         <v>1966</v>
@@ -15640,12 +15646,12 @@
         <v>1983</v>
       </c>
       <c r="B1116" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B1117" t="s">
         <v>1985</v>
@@ -15656,20 +15662,20 @@
         <v>1986</v>
       </c>
       <c r="B1118" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B1119" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B1120" t="s">
         <v>1989</v>
@@ -15704,12 +15710,12 @@
         <v>1996</v>
       </c>
       <c r="B1124" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="B1125" t="s">
         <v>1998</v>
@@ -15720,12 +15726,12 @@
         <v>1999</v>
       </c>
       <c r="B1126" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B1127" t="s">
         <v>2001</v>
@@ -15880,12 +15886,12 @@
         <v>2038</v>
       </c>
       <c r="B1146" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B1147" t="s">
         <v>2040</v>
@@ -15896,12 +15902,12 @@
         <v>2041</v>
       </c>
       <c r="B1148" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B1149" t="s">
         <v>2043</v>
@@ -15912,12 +15918,12 @@
         <v>2044</v>
       </c>
       <c r="B1150" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="B1151" t="s">
         <v>2046</v>
@@ -15936,28 +15942,28 @@
         <v>2049</v>
       </c>
       <c r="B1153" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="B1154" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="B1155" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="B1156" t="s">
         <v>2053</v>
@@ -16040,12 +16046,12 @@
         <v>2072</v>
       </c>
       <c r="B1166" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B1167" t="s">
         <v>2074</v>
@@ -16088,20 +16094,20 @@
         <v>2083</v>
       </c>
       <c r="B1172" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="B1173" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="B1174" t="s">
         <v>2086</v>
@@ -16136,12 +16142,12 @@
         <v>2093</v>
       </c>
       <c r="B1178" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="B1179" t="s">
         <v>2095</v>
@@ -16168,28 +16174,28 @@
         <v>2100</v>
       </c>
       <c r="B1182" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B1183" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B1184" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="B1185" t="s">
         <v>2104</v>
@@ -16208,12 +16214,12 @@
         <v>2107</v>
       </c>
       <c r="B1187" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="B1188" t="s">
         <v>2109</v>
@@ -16232,19 +16238,27 @@
         <v>2112</v>
       </c>
       <c r="B1190" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="B1191" t="s">
         <v>2114</v>
       </c>
     </row>
+    <row r="1192" spans="1:2">
+      <c r="A1192" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>2116</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1191"/>
+  <autoFilter ref="A1:B1192"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2119">
   <si>
     <t>en</t>
   </si>
@@ -2258,6 +2258,12 @@
   </si>
   <si>
     <t>Šriftas (Orange)</t>
+  </si>
+  <si>
+    <t>Font (Pale Oak)</t>
+  </si>
+  <si>
+    <t>Šriftas („Pale Oak“)</t>
   </si>
   <si>
     <t>Font (Pink)</t>
@@ -6714,7 +6720,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1192"/>
+  <dimension ref="A1:B1193"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -10206,28 +10212,28 @@
         <v>789</v>
       </c>
       <c r="B436" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B437" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B438" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B439" t="s">
         <v>793</v>
@@ -10326,12 +10332,12 @@
         <v>816</v>
       </c>
       <c r="B451" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B452" t="s">
         <v>818</v>
@@ -10342,12 +10348,12 @@
         <v>819</v>
       </c>
       <c r="B453" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B454" t="s">
         <v>821</v>
@@ -10462,12 +10468,12 @@
         <v>848</v>
       </c>
       <c r="B468" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B469" t="s">
         <v>850</v>
@@ -10478,20 +10484,20 @@
         <v>851</v>
       </c>
       <c r="B470" t="s">
-        <v>565</v>
+        <v>852</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B471" t="s">
-        <v>852</v>
+        <v>565</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B472" t="s">
         <v>854</v>
@@ -10502,12 +10508,12 @@
         <v>855</v>
       </c>
       <c r="B473" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B474" t="s">
         <v>857</v>
@@ -10526,23 +10532,23 @@
         <v>860</v>
       </c>
       <c r="B476" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B477" t="s">
-        <v>565</v>
+        <v>862</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B478" t="s">
-        <v>863</v>
+        <v>565</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -10550,12 +10556,12 @@
         <v>864</v>
       </c>
       <c r="B479" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B480" t="s">
         <v>866</v>
@@ -10606,20 +10612,20 @@
         <v>877</v>
       </c>
       <c r="B486" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B487" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B488" t="s">
         <v>880</v>
@@ -10630,12 +10636,12 @@
         <v>881</v>
       </c>
       <c r="B489" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B490" t="s">
         <v>883</v>
@@ -10646,28 +10652,28 @@
         <v>884</v>
       </c>
       <c r="B491" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B492" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B493" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B494" t="s">
         <v>888</v>
@@ -10854,12 +10860,12 @@
         <v>933</v>
       </c>
       <c r="B517" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B518" t="s">
         <v>935</v>
@@ -11006,12 +11012,12 @@
         <v>970</v>
       </c>
       <c r="B536" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B537" t="s">
         <v>972</v>
@@ -11030,20 +11036,20 @@
         <v>975</v>
       </c>
       <c r="B539" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B540" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B541" t="s">
         <v>978</v>
@@ -11062,28 +11068,28 @@
         <v>981</v>
       </c>
       <c r="B543" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B544" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B545" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B546" t="s">
         <v>985</v>
@@ -11118,20 +11124,20 @@
         <v>992</v>
       </c>
       <c r="B550" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B551" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B552" t="s">
         <v>995</v>
@@ -11142,12 +11148,12 @@
         <v>996</v>
       </c>
       <c r="B553" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B554" t="s">
         <v>998</v>
@@ -11158,12 +11164,12 @@
         <v>999</v>
       </c>
       <c r="B555" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B556" t="s">
         <v>1001</v>
@@ -11262,12 +11268,12 @@
         <v>1024</v>
       </c>
       <c r="B568" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B569" t="s">
         <v>1026</v>
@@ -11294,12 +11300,12 @@
         <v>1031</v>
       </c>
       <c r="B572" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B573" t="s">
         <v>1033</v>
@@ -11350,12 +11356,12 @@
         <v>1044</v>
       </c>
       <c r="B579" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B580" t="s">
         <v>1046</v>
@@ -11366,28 +11372,28 @@
         <v>1047</v>
       </c>
       <c r="B581" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B582" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B583" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B584" t="s">
         <v>1051</v>
@@ -11534,12 +11540,12 @@
         <v>1086</v>
       </c>
       <c r="B602" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B603" t="s">
         <v>1088</v>
@@ -11606,28 +11612,28 @@
         <v>1103</v>
       </c>
       <c r="B611" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B612" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B613" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B614" t="s">
         <v>1107</v>
@@ -11758,12 +11764,12 @@
         <v>1138</v>
       </c>
       <c r="B630" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B631" t="s">
         <v>1140</v>
@@ -11782,12 +11788,12 @@
         <v>1143</v>
       </c>
       <c r="B633" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B634" t="s">
         <v>1145</v>
@@ -11822,12 +11828,12 @@
         <v>1152</v>
       </c>
       <c r="B638" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B639" t="s">
         <v>1154</v>
@@ -11838,12 +11844,12 @@
         <v>1155</v>
       </c>
       <c r="B640" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B641" t="s">
         <v>1157</v>
@@ -11862,52 +11868,52 @@
         <v>1160</v>
       </c>
       <c r="B643" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B644" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B645" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B646" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B647" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B648" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B649" t="s">
         <v>1167</v>
@@ -11918,36 +11924,36 @@
         <v>1168</v>
       </c>
       <c r="B650" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B651" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B652" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B653" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B654" t="s">
         <v>1173</v>
@@ -11982,28 +11988,28 @@
         <v>1180</v>
       </c>
       <c r="B658" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B659" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B660" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B661" t="s">
         <v>1184</v>
@@ -12014,12 +12020,12 @@
         <v>1185</v>
       </c>
       <c r="B662" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B663" t="s">
         <v>1187</v>
@@ -12214,12 +12220,12 @@
         <v>1234</v>
       </c>
       <c r="B687" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B688" t="s">
         <v>1236</v>
@@ -12246,20 +12252,20 @@
         <v>1241</v>
       </c>
       <c r="B691" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B692" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B693" t="s">
         <v>1244</v>
@@ -12390,12 +12396,12 @@
         <v>1275</v>
       </c>
       <c r="B709" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B710" t="s">
         <v>1277</v>
@@ -12406,20 +12412,20 @@
         <v>1278</v>
       </c>
       <c r="B711" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B712" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B713" t="s">
         <v>1281</v>
@@ -12430,28 +12436,28 @@
         <v>1282</v>
       </c>
       <c r="B714" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B715" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B716" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B717" t="s">
         <v>1286</v>
@@ -12470,20 +12476,20 @@
         <v>1289</v>
       </c>
       <c r="B719" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B720" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B721" t="s">
         <v>1292</v>
@@ -12582,20 +12588,20 @@
         <v>1315</v>
       </c>
       <c r="B733" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B734" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B735" t="s">
         <v>1318</v>
@@ -12638,12 +12644,12 @@
         <v>1327</v>
       </c>
       <c r="B740" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B741" t="s">
         <v>1329</v>
@@ -12694,12 +12700,12 @@
         <v>1340</v>
       </c>
       <c r="B747" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B748" t="s">
         <v>1342</v>
@@ -12726,20 +12732,20 @@
         <v>1347</v>
       </c>
       <c r="B751" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B752" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B753" t="s">
         <v>1350</v>
@@ -12758,20 +12764,20 @@
         <v>1353</v>
       </c>
       <c r="B755" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B756" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B757" t="s">
         <v>1356</v>
@@ -12878,28 +12884,28 @@
         <v>1381</v>
       </c>
       <c r="B770" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B771" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B772" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B773" t="s">
         <v>1385</v>
@@ -12942,12 +12948,12 @@
         <v>1394</v>
       </c>
       <c r="B778" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B779" t="s">
         <v>1396</v>
@@ -13054,28 +13060,28 @@
         <v>1421</v>
       </c>
       <c r="B792" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B793" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B794" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B795" t="s">
         <v>1425</v>
@@ -13094,12 +13100,12 @@
         <v>1428</v>
       </c>
       <c r="B797" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B798" t="s">
         <v>1430</v>
@@ -13118,12 +13124,12 @@
         <v>1433</v>
       </c>
       <c r="B800" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B801" t="s">
         <v>1435</v>
@@ -13142,28 +13148,28 @@
         <v>1438</v>
       </c>
       <c r="B803" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B804" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B805" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B806" t="s">
         <v>1442</v>
@@ -13174,20 +13180,20 @@
         <v>1443</v>
       </c>
       <c r="B807" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B808" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B809" t="s">
         <v>1446</v>
@@ -13254,20 +13260,20 @@
         <v>1461</v>
       </c>
       <c r="B817" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B818" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B819" t="s">
         <v>1464</v>
@@ -13302,12 +13308,12 @@
         <v>1471</v>
       </c>
       <c r="B823" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B824" t="s">
         <v>1473</v>
@@ -13326,12 +13332,12 @@
         <v>1476</v>
       </c>
       <c r="B826" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B827" t="s">
         <v>1478</v>
@@ -13350,12 +13356,12 @@
         <v>1481</v>
       </c>
       <c r="B829" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B830" t="s">
         <v>1483</v>
@@ -13382,12 +13388,12 @@
         <v>1488</v>
       </c>
       <c r="B833" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B834" t="s">
         <v>1490</v>
@@ -13398,12 +13404,12 @@
         <v>1491</v>
       </c>
       <c r="B835" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B836" t="s">
         <v>1493</v>
@@ -13446,36 +13452,36 @@
         <v>1502</v>
       </c>
       <c r="B841" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B842" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B843" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B844" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B845" t="s">
         <v>1507</v>
@@ -13542,28 +13548,28 @@
         <v>1522</v>
       </c>
       <c r="B853" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B854" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B855" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B856" t="s">
         <v>1526</v>
@@ -13670,20 +13676,20 @@
         <v>1551</v>
       </c>
       <c r="B869" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B870" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B871" t="s">
         <v>1554</v>
@@ -13702,12 +13708,12 @@
         <v>1557</v>
       </c>
       <c r="B873" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B874" t="s">
         <v>1559</v>
@@ -13718,12 +13724,12 @@
         <v>1560</v>
       </c>
       <c r="B875" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B876" t="s">
         <v>1562</v>
@@ -13846,20 +13852,20 @@
         <v>1591</v>
       </c>
       <c r="B891" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B892" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B893" t="s">
         <v>1594</v>
@@ -13886,12 +13892,12 @@
         <v>1599</v>
       </c>
       <c r="B896" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B897" t="s">
         <v>1601</v>
@@ -13910,12 +13916,12 @@
         <v>1604</v>
       </c>
       <c r="B899" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B900" t="s">
         <v>1606</v>
@@ -13926,12 +13932,12 @@
         <v>1607</v>
       </c>
       <c r="B901" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B902" t="s">
         <v>1609</v>
@@ -13942,12 +13948,12 @@
         <v>1610</v>
       </c>
       <c r="B903" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B904" t="s">
         <v>1612</v>
@@ -13958,12 +13964,12 @@
         <v>1613</v>
       </c>
       <c r="B905" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B906" t="s">
         <v>1615</v>
@@ -14022,12 +14028,12 @@
         <v>1628</v>
       </c>
       <c r="B913" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B914" t="s">
         <v>1630</v>
@@ -14054,12 +14060,12 @@
         <v>1635</v>
       </c>
       <c r="B917" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B918" t="s">
         <v>1637</v>
@@ -14070,20 +14076,20 @@
         <v>1638</v>
       </c>
       <c r="B919" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B920" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B921" t="s">
         <v>1641</v>
@@ -14094,12 +14100,12 @@
         <v>1642</v>
       </c>
       <c r="B922" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B923" t="s">
         <v>1644</v>
@@ -14134,28 +14140,28 @@
         <v>1651</v>
       </c>
       <c r="B927" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B928" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B929" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B930" t="s">
         <v>1655</v>
@@ -14198,20 +14204,20 @@
         <v>1664</v>
       </c>
       <c r="B935" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B936" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B937" t="s">
         <v>1667</v>
@@ -14246,12 +14252,12 @@
         <v>1674</v>
       </c>
       <c r="B941" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B942" t="s">
         <v>1676</v>
@@ -14262,20 +14268,20 @@
         <v>1677</v>
       </c>
       <c r="B943" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B944" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B945" t="s">
         <v>1680</v>
@@ -14366,20 +14372,20 @@
         <v>1701</v>
       </c>
       <c r="B956" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B957" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B958" t="s">
         <v>1704</v>
@@ -14398,12 +14404,12 @@
         <v>1707</v>
       </c>
       <c r="B960" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B961" t="s">
         <v>1709</v>
@@ -14414,28 +14420,28 @@
         <v>1710</v>
       </c>
       <c r="B962" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B963" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B964" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B965" t="s">
         <v>1714</v>
@@ -14478,20 +14484,20 @@
         <v>1723</v>
       </c>
       <c r="B970" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B971" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B972" t="s">
         <v>1726</v>
@@ -14550,20 +14556,20 @@
         <v>1739</v>
       </c>
       <c r="B979" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B980" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B981" t="s">
         <v>1742</v>
@@ -14662,20 +14668,20 @@
         <v>1765</v>
       </c>
       <c r="B993" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B994" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B995" t="s">
         <v>1768</v>
@@ -14710,12 +14716,12 @@
         <v>1775</v>
       </c>
       <c r="B999" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B1000" t="s">
         <v>1777</v>
@@ -14726,12 +14732,12 @@
         <v>1778</v>
       </c>
       <c r="B1001" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B1002" t="s">
         <v>1780</v>
@@ -14742,15 +14748,15 @@
         <v>1781</v>
       </c>
       <c r="B1003" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B1004" t="s">
         <v>1782</v>
-      </c>
-      <c r="B1004" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
@@ -14774,12 +14780,12 @@
         <v>1788</v>
       </c>
       <c r="B1007" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B1008" t="s">
         <v>1790</v>
@@ -14798,12 +14804,12 @@
         <v>1793</v>
       </c>
       <c r="B1010" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B1011" t="s">
         <v>1795</v>
@@ -14862,20 +14868,20 @@
         <v>1808</v>
       </c>
       <c r="B1018" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1019" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B1020" t="s">
         <v>1811</v>
@@ -14894,12 +14900,12 @@
         <v>1814</v>
       </c>
       <c r="B1022" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1023" t="s">
         <v>1816</v>
@@ -14910,20 +14916,20 @@
         <v>1817</v>
       </c>
       <c r="B1024" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1025" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B1026" t="s">
         <v>1820</v>
@@ -14958,20 +14964,20 @@
         <v>1827</v>
       </c>
       <c r="B1030" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1031" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1032" t="s">
         <v>1830</v>
@@ -14990,12 +14996,12 @@
         <v>1833</v>
       </c>
       <c r="B1034" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1035" t="s">
         <v>1835</v>
@@ -15046,12 +15052,12 @@
         <v>1846</v>
       </c>
       <c r="B1041" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="B1042" t="s">
         <v>1848</v>
@@ -15086,12 +15092,12 @@
         <v>1855</v>
       </c>
       <c r="B1046" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1047" t="s">
         <v>1857</v>
@@ -15102,12 +15108,12 @@
         <v>1858</v>
       </c>
       <c r="B1048" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B1049" t="s">
         <v>1860</v>
@@ -15126,12 +15132,12 @@
         <v>1863</v>
       </c>
       <c r="B1051" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B1052" t="s">
         <v>1865</v>
@@ -15158,12 +15164,12 @@
         <v>1870</v>
       </c>
       <c r="B1055" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B1056" t="s">
         <v>1872</v>
@@ -15310,12 +15316,12 @@
         <v>1907</v>
       </c>
       <c r="B1074" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B1075" t="s">
         <v>1909</v>
@@ -15390,12 +15396,12 @@
         <v>1926</v>
       </c>
       <c r="B1084" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1085" t="s">
         <v>1928</v>
@@ -15414,12 +15420,12 @@
         <v>1931</v>
       </c>
       <c r="B1087" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B1088" t="s">
         <v>1933</v>
@@ -15430,12 +15436,12 @@
         <v>1934</v>
       </c>
       <c r="B1089" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B1090" t="s">
         <v>1936</v>
@@ -15446,12 +15452,12 @@
         <v>1937</v>
       </c>
       <c r="B1091" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="B1092" t="s">
         <v>1939</v>
@@ -15470,12 +15476,12 @@
         <v>1942</v>
       </c>
       <c r="B1094" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B1095" t="s">
         <v>1944</v>
@@ -15494,12 +15500,12 @@
         <v>1947</v>
       </c>
       <c r="B1097" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="B1098" t="s">
         <v>1949</v>
@@ -15574,12 +15580,12 @@
         <v>1966</v>
       </c>
       <c r="B1107" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B1108" t="s">
         <v>1968</v>
@@ -15654,12 +15660,12 @@
         <v>1985</v>
       </c>
       <c r="B1117" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B1118" t="s">
         <v>1987</v>
@@ -15670,20 +15676,20 @@
         <v>1988</v>
       </c>
       <c r="B1119" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B1120" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B1121" t="s">
         <v>1991</v>
@@ -15718,12 +15724,12 @@
         <v>1998</v>
       </c>
       <c r="B1125" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B1126" t="s">
         <v>2000</v>
@@ -15734,12 +15740,12 @@
         <v>2001</v>
       </c>
       <c r="B1127" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B1128" t="s">
         <v>2003</v>
@@ -15894,12 +15900,12 @@
         <v>2040</v>
       </c>
       <c r="B1147" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B1148" t="s">
         <v>2042</v>
@@ -15910,12 +15916,12 @@
         <v>2043</v>
       </c>
       <c r="B1149" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B1150" t="s">
         <v>2045</v>
@@ -15926,12 +15932,12 @@
         <v>2046</v>
       </c>
       <c r="B1151" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="B1152" t="s">
         <v>2048</v>
@@ -15950,28 +15956,28 @@
         <v>2051</v>
       </c>
       <c r="B1154" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="B1155" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="B1156" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="B1157" t="s">
         <v>2055</v>
@@ -16054,12 +16060,12 @@
         <v>2074</v>
       </c>
       <c r="B1167" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="B1168" t="s">
         <v>2076</v>
@@ -16102,20 +16108,20 @@
         <v>2085</v>
       </c>
       <c r="B1173" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="B1174" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="B1175" t="s">
         <v>2088</v>
@@ -16150,12 +16156,12 @@
         <v>2095</v>
       </c>
       <c r="B1179" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="B1180" t="s">
         <v>2097</v>
@@ -16182,28 +16188,28 @@
         <v>2102</v>
       </c>
       <c r="B1183" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="B1184" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="B1185" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="B1186" t="s">
         <v>2106</v>
@@ -16222,12 +16228,12 @@
         <v>2109</v>
       </c>
       <c r="B1188" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="B1189" t="s">
         <v>2111</v>
@@ -16246,19 +16252,27 @@
         <v>2114</v>
       </c>
       <c r="B1191" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="B1192" t="s">
         <v>2116</v>
       </c>
     </row>
+    <row r="1193" spans="1:2">
+      <c r="A1193" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>2118</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1192"/>
+  <autoFilter ref="A1:B1193"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
